--- a/reports/report_2026-09-13.xlsx
+++ b/reports/report_2026-09-13.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>google data analytics apprenticeship</t>
+          <t>Show HN: Dbmask – Discover, mask, and verify sensitive data in SQL databases</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,16 +465,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+apprenticeship</t>
+          <t>https://github.com/sealandseacat/dbmask</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>dbt biocare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -493,16 +493,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.368987975951904</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+biocare</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The EPA is planning to scrap public review rules for data center pollution</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.368987975951904</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://capitalbnews.org/data-centers-permit-rules-epa/</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>what is dbt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "google data analytics apprenticeship" (and what it should mean for your 2026 content plan)</t>
+          <t>What Show HN: Dbmask – Discover, mask, and verify sensitive data in SQL databases means for analytics people (a quick take)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>google data analytics apprenticeship</t>
+          <t>Show HN: Dbmask – Discover, mask, and verify sensitive data in SQL databases</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -796,11 +796,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+apprenticeship</t>
+          <t>https://github.com/sealandseacat/dbmask</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Data Pipeline, explained in plain English (a 2026 beginner's guide)</t>
+          <t>Why everyone's suddenly talking about "dbt biocare" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>dbt biocare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -824,11 +824,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.368987975951904</v>
+        <v>1.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+biocare</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What The EPA is planning to scrap public review rules for data center pollution means for analytics people (a quick take)</t>
+          <t>Data Pipeline, explained in plain English (a 2026 beginner's guide)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The EPA is planning to scrap public review rules for data center pollution</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -852,11 +852,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.2</v>
+        <v>1.368987975951904</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://capitalbnews.org/data-centers-permit-rules-epa/</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "power bi dashboard" (and what it should mean for your 2026 content plan)</t>
+          <t>dbt, explained in plain English (a 2026 beginner's guide)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>what is dbt</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F430"/>
+  <dimension ref="A1:F418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>google data analytics apprenticeship</t>
+          <t>Show HN: Dbmask – Discover, mask, and verify sensitive data in SQL databases</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+apprenticeship</t>
+          <t>https://github.com/sealandseacat/dbmask</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>what is data pipeline</t>
+          <t>dbt biocare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.368987975951904</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+biocare</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The EPA is planning to scrap public review rules for data center pollution</t>
+          <t>what is data pipeline</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1173,16 +1173,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.368987975951904</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://capitalbnews.org/data-centers-permit-rules-epa/</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>what is dbt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>what is dbt</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.7301338792878506</v>
+        <v>0.7301045701784317</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>data engineering projects</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.6625751503006012</v>
+        <v>0.6776052104208418</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+projects</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.658817635270541</v>
+        <v>0.6625751503006012</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>what is a data pipeline</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1677,16 +1677,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.6583166332665331</v>
+        <v>0.658817635270541</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+a+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dbt labs</t>
+          <t>what is a data pipeline</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1705,16 +1705,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.655060120240481</v>
+        <v>0.6583166332665331</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+labs</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+a+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>dbt labs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6437875751503006</v>
+        <v>0.655060120240481</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+labs</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6400300601202404</v>
+        <v>0.6437875751503006</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.6362725450901803</v>
+        <v>0.6400300601202404</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>data engineering zoomcamp</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.6287575150300601</v>
+        <v>0.6362725450901803</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+zoomcamp</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>what is dbt in data engineering</t>
+          <t>data engineering zoomcamp</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.625</v>
+        <v>0.6287575150300601</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt+in+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>what is dbt in data engineering</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1929,16 +1929,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5539511450994561</v>
+        <v>0.625</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>We rebuilt the old Google Analytics on top of GA4's data</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1957,16 +1957,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>suggest</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+management</t>
+          <t>https://github.com/adacahq/adaca-analytics</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1985,16 +1985,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.5</v>
+        <v>0.5539289083355077</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>suggest</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=etl+vs+data+pipeline</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+pipeline</t>
+          <t>https://www.google.com/search?q=how+to+data+analytics+work</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>how to dbt</t>
+          <t>how to data analytics</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+dbt</t>
+          <t>https://www.google.com/search?q=how+to+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=etl+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+snowflake</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+delete+data+analytics+from+iphone</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+dashboard</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+sql</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dbt vs sqlmesh</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+sqlmesh</t>
+          <t>https://www.google.com/search?q=how+to+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>dbt vs spark</t>
+          <t>how to dbt</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+spark</t>
+          <t>https://www.google.com/search?q=how+to+dbt</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+design+data+pipeline</t>
+          <t>https://www.google.com/search?q=how+to+delete+data+analytics+from+iphone</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+do+data+analytics</t>
+          <t>https://www.google.com/search?q=how+to+design+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+get+into+data+engineering</t>
+          <t>https://www.google.com/search?q=visual+studio+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>vs data analytics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+analytics+engineering</t>
+          <t>https://www.google.com/search?q=vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>vs dbt</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+data+analytics</t>
+          <t>https://www.google.com/search?q=vs+dbt</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>vs power bi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+data+analytics+for+free</t>
+          <t>https://www.google.com/search?q=vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>what is ai in analytics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+pro</t>
+          <t>https://www.google.com/search?q=what+is+ai+in+analytics</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+learn+data+analytics+for+free</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>exabeam ai agent analytics</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=exabeam+ai+agent+analytics</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+in+accounting</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+desktop</t>
+          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline+fabric</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>what is power bi and tableau</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+and+tableau</t>
+          <t>https://www.google.com/search?q=dataops+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+master+data+engineering</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+in+healthcare</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=mlops+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+in+simple+words</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+analytics+work</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+job</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+sql</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+salary</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+training</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+used+for</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>power bi vs tableau</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+vs+tableau</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=excel+vs+power+bi</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+all+about</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+python</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+and+analytics</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+optimize+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+and+data+science</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>what is dbt labs</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+labs</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>what is dbt models</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+models</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+in+simple+words</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>what is dbt in snowflake</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+in+snowflake</t>
+          <t>https://www.google.com/search?q=etl+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+llm+analytics</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+role</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>what is dbt fusion</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+fusion</t>
+          <t>https://www.google.com/search?q=what+is+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=fabric+vs+power+bi</t>
+          <t>https://www.google.com/search?q=what+is+analytics+engineering+dbt</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+and+how+does+it+work</t>
+          <t>https://www.google.com/search?q=what+is+analytics+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>what is dbt data</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+data</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+and+visualization</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=grafana+vs+power+bi</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+big+data+analytics</t>
+          <t>https://www.google.com/search?q=etl+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+testing</t>
+          <t>https://www.google.com/search?q=how+to+learn+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>exabeam ai agent analytics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+databricks</t>
+          <t>https://www.google.com/search?q=exabeam+ai+agent+analytics</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=devops+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=excel+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+analytics</t>
+          <t>https://www.google.com/search?q=fabric+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+orchestration</t>
+          <t>https://www.google.com/search?q=glue+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>dbt vs databricks</t>
+          <t>dbt vs sqlmesh</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+databricks</t>
+          <t>https://www.google.com/search?q=dbt+vs+sqlmesh</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>dbt vs snowflake</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+snowflake</t>
+          <t>https://www.google.com/search?q=devops+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+benchmark</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>workflow vs data pipeline</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+comparison</t>
+          <t>https://www.google.com/search?q=workflow+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>why power bi over tableau</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=glue+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=why+power+bi+over+tableau</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>why dbt is used</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt+is+used</t>
+          <t>https://www.google.com/search?q=why+power+bi+over+excel</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>why dbt app is not working</t>
+          <t>why power bi is used</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt+app+is+not+working</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+used</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>why dbt</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+not+available+for+mac</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>why power bi is important</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+pipeline</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+important</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+reddit</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+better+than+tableau</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+reddit</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+better+than+excel</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+master+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>why data analytics</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+interview+questions</t>
+          <t>https://www.google.com/search?q=why+data+analytics</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi+bas</t>
+          <t>https://www.google.com/search?q=top+data+pipeline+solutions</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ai agent analytics dashboard servicenow</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard+servicenow</t>
+          <t>https://www.google.com/search?q=tableau+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ai agent analytics dashboard</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard</t>
+          <t>https://www.google.com/search?q=statistics+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ai agent analytics</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics</t>
+          <t>https://www.google.com/search?q=software+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>power bi courses</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+courses</t>
+          <t>https://www.google.com/search?q=or+power+bi+symbol</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>or power bi measure</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+certification</t>
+          <t>https://www.google.com/search?q=or+power+bi+measure</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>or power bi dax</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=software+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=or+power+bi+dax</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+analytics+engineering+reddit</t>
+          <t>https://www.google.com/search?q=why+power+bi+gateway+went+offline</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+analytics+engineering+dbt</t>
+          <t>https://www.google.com/search?q=why+data+engineering+interview+questions</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ai agent analytics platform</t>
+          <t>why dbt app is not working</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+platform</t>
+          <t>https://www.google.com/search?q=why+dbt+app+is+not+working</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ai in analytics course</t>
+          <t>why dbt</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+in+analytics+course</t>
+          <t>https://www.google.com/search?q=why+dbt</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ai in analytics</t>
+          <t>why data pipeline</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+in+analytics</t>
+          <t>https://www.google.com/search?q=why+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>ai vs data engineering</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+used</t>
+          <t>https://www.google.com/search?q=ai+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>ai vs data analytics</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+ai</t>
+          <t>https://www.google.com/search?q=ai+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>ai in analytics course</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+development</t>
+          <t>https://www.google.com/search?q=ai+in+analytics+course</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>ai in analytics</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+architecture</t>
+          <t>https://www.google.com/search?q=ai+in+analytics</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>analytics engineering vs data engineering</t>
+          <t>power bi</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=power+bi</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>analytics engineering salary</t>
+          <t>ai agent analytics servicenow</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+salary</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+servicenow</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>why dbt is used in data engineering</t>
+          <t>ai agent analytics platform</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt+is+used+in+data+engineering</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+platform</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>best data engineering blogs</t>
+          <t>ai agent analytics dashboard servicenow</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+blogs</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard+servicenow</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>best data analytics tools</t>
+          <t>ai agent analytics dashboard</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+tools</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>best data analytics software</t>
+          <t>ai agent analytics</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+software</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>best data analytics programs</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+programs</t>
+          <t>https://www.google.com/search?q=why+data+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ai agent analytics vidhya</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+vidhya</t>
+          <t>https://www.google.com/search?q=why+data+engineering+is+important</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>power bi courses</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+the+future</t>
+          <t>https://www.google.com/search?q=power+bi+courses</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>power bi certification</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+gateway+went+offline</t>
+          <t>https://www.google.com/search?q=power+bi+certification</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>why power bi</t>
+          <t>ai agent analytics vidhya</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+vidhya</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>best data engineering books</t>
+          <t>llm analytics</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+books</t>
+          <t>https://www.google.com/search?q=llm+analytics</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+engineering</t>
+          <t>https://www.google.com/search?q=integration+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>use of ai in analytics</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+analytics</t>
+          <t>https://www.google.com/search?q=use+of+ai+in+analytics</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+login</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+python</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+download</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+databricks</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+desktop+download</t>
+          <t>https://www.google.com/search?q=how+to+big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics</t>
+          <t>https://www.google.com/search?q=grafana+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+sql</t>
+          <t>https://www.google.com/search?q=how+to+study+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>or power bi</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+snowflake</t>
+          <t>https://www.google.com/search?q=or+power+bi</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+analytics+engineering</t>
+          <t>https://www.google.com/search?q=how+to+power+bi+youtube</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=integration+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=how+to+power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+study+data+analytics</t>
+          <t>https://www.google.com/search?q=how+to+power+bi+bas</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>how to power bi</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+start+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+power+bi</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi+youtube</t>
+          <t>https://www.google.com/search?q=how+to+optimize+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi+dashboard</t>
+          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi</t>
+          <t>https://www.google.com/search?q=how+to+master+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi+dax</t>
+          <t>https://www.google.com/search?q=how+to+learn+python+for+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi</t>
+          <t>https://www.google.com/search?q=how+to+start+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+python</t>
+          <t>https://www.google.com/search?q=mlops+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>what is ai in analytics</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+ai+in+analytics</t>
+          <t>https://www.google.com/search?q=looker+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=vs+power+bi</t>
+          <t>https://www.google.com/search?q=llm+analytics+vidhya</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>vs dbt</t>
+          <t>power bi vs tableau</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=vs+dbt</t>
+          <t>https://www.google.com/search?q=power+bi+vs+tableau</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>power bi training</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=vs+data+analytics</t>
+          <t>https://www.google.com/search?q=power+bi+training</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>power bi login</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=visual+studio+data+pipeline</t>
+          <t>https://www.google.com/search?q=power+bi+login</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi</t>
+          <t>https://www.google.com/search?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi+symbol</t>
+          <t>https://www.google.com/search?q=how+to+learn+data+analytics</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+master+data+analytics</t>
+          <t>https://www.google.com/search?q=llm+analytics+benchmark</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+etl</t>
+          <t>https://www.google.com/search?q=how+to+get+into+data+engineering</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=looker+vs+power+bi</t>
+          <t>https://www.google.com/search?q=how+to+do+data+analytics</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+vidhya</t>
+          <t>https://www.google.com/search?q=llm+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+tools</t>
+          <t>https://www.google.com/search?q=llm+analytics+posthog</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+posthog</t>
+          <t>https://www.google.com/search?q=llm+analytics+platform</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+platform</t>
+          <t>https://www.google.com/search?q=llm+analytics+meaning</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+meaning</t>
+          <t>https://www.google.com/search?q=llm+analytics+leaderboard</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+leaderboard</t>
+          <t>https://www.google.com/search?q=llm+analytics+dashboard</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+machine+learning</t>
+          <t>https://www.google.com/search?q=llm+analytics+comparison</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+python+for+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+learn+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>backend vs data engineering</t>
+          <t>api vs data pipeline</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=backend+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=api+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>best ai agent analytics tools</t>
+          <t>backend vs data engineering</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+ai+agent+analytics+tools</t>
+          <t>https://www.google.com/search?q=backend+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>best analytics engineering books</t>
+          <t>best ai agent analytics tools</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+analytics+engineering+books</t>
+          <t>https://www.google.com/search?q=best+ai+agent+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>best analytics engineering books</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+better+than+tableau</t>
+          <t>https://www.google.com/search?q=best+analytics+engineering+books</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>best analytics engineering course</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+important</t>
+          <t>https://www.google.com/search?q=best+analytics+engineering+course</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>best data analytics books</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+not+available+for+mac</t>
+          <t>https://www.google.com/search?q=best+data+analytics+books</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>best data analytics bootcamp</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+used</t>
+          <t>https://www.google.com/search?q=best+data+analytics+bootcamp</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ai agent analytics servicenow</t>
+          <t>best data analytics certification</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+servicenow</t>
+          <t>https://www.google.com/search?q=best+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>best data analytics certification reddit</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+and+visualization</t>
+          <t>https://www.google.com/search?q=best+data+analytics+certification+reddit</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>best data analytics courses reddit</t>
+          <t>best data analytics courses</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+courses+reddit</t>
+          <t>https://www.google.com/search?q=best+data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>best power bi courses</t>
+          <t>best data analytics courses reddit</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+courses</t>
+          <t>https://www.google.com/search?q=best+data+analytics+courses+reddit</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>best power bi dashboards</t>
+          <t>analytics engineering</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+dashboards</t>
+          <t>https://www.google.com/search?q=analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>best power bi training</t>
+          <t>best dbt training for therapists</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+training</t>
+          <t>https://www.google.com/search?q=best+dbt+training+for+therapists</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>best power bi tutorial on youtube</t>
+          <t>best power bi books</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+tutorial+on+youtube</t>
+          <t>https://www.google.com/search?q=best+power+bi+books</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>best power bi visuals</t>
+          <t>best power bi certification</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+visuals</t>
+          <t>https://www.google.com/search?q=best+power+bi+certification</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>why dbt is used</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=tableau+vs+power+bi</t>
+          <t>https://www.google.com/search?q=why+dbt+is+used</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>best dbt apps</t>
+          <t>best data pipeline development services</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+apps</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+development+services</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>cloud vs data engineering</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics</t>
+          <t>https://www.google.com/search?q=cloud+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>cybersecurity vs data engineering</t>
+          <t>business vs data analytics</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=cybersecurity+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=business+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>cybersecurity vs data analytics</t>
+          <t>best power bi visuals</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=cybersecurity+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=best+power+bi+visuals</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>cloud vs data engineering</t>
+          <t>best data engineering podcasts</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=cloud+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=best+data+engineering+podcasts</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>best data pipeline</t>
+          <t>best data engineering courses</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline</t>
+          <t>https://www.google.com/search?q=best+data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>best data pipeline development services</t>
+          <t>best data engineering course reddit</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+development+services</t>
+          <t>https://www.google.com/search?q=best+data+engineering+course+reddit</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>best data engineering bootcamp</t>
+          <t>best power bi course for beginners</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+bootcamp</t>
+          <t>https://www.google.com/search?q=best+power+bi+course+for+beginners</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>api vs data pipeline</t>
+          <t>best data engineering certifications</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=api+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=best+data+engineering+certifications</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>and data analytics</t>
+          <t>best data engineering bootcamp</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=and+data+analytics</t>
+          <t>https://www.google.com/search?q=best+data+engineering+bootcamp</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>analytics vs data engineering</t>
+          <t>best data engineering books</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=best+data+engineering+books</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>analytics engineering with sql and dbt pdf</t>
+          <t>best data engineering blogs</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt+pdf</t>
+          <t>https://www.google.com/search?q=best+data+engineering+blogs</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>analytics engineering with sql and dbt</t>
+          <t>best data analytics tools</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt</t>
+          <t>https://www.google.com/search?q=best+data+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>analytics engineering vs data science</t>
+          <t>best data analytics software</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+vs+data+science</t>
+          <t>https://www.google.com/search?q=best+data+analytics+software</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>best data engineering certifications 2026</t>
+          <t>best data analytics programs</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+certifications+2026</t>
+          <t>https://www.google.com/search?q=best+data+analytics+programs</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>best data engineering certifications</t>
+          <t>best data analytics masters programs</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+certifications</t>
+          <t>https://www.google.com/search?q=best+data+analytics+masters+programs</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>best data pipeline architecture</t>
+          <t>best data engineering certifications 2026</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+architecture</t>
+          <t>https://www.google.com/search?q=best+data+engineering+certifications+2026</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>why data engineering</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+over+tableau</t>
+          <t>https://www.google.com/search?q=why+data+engineering</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>analytics engineering manager</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+manager</t>
+          <t>https://www.google.com/search?q=why+data+analytics+reddit</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>analytics engineering jobs</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+jobs</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+used</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>analytics engineering course</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+course</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+the+future+of+everything</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>analytics engineering best practices</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+best+practices</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+the+future</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>analytics engineering</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+important</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ai vs data engineering</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+a+good+career</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>why data analytics course</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi+measure</t>
+          <t>https://www.google.com/search?q=why+data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>best data analytics masters programs</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+masters+programs</t>
+          <t>https://www.google.com/search?q=why+data+analytics+as+a+career</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+better+than+excel</t>
+          <t>https://www.google.com/search?q=power+bi+desktop+download</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>analytics engineering podcast</t>
+          <t>analytics engineering best practices</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+podcast</t>
+          <t>https://www.google.com/search?q=analytics+engineering+best+practices</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ai vs data analytics</t>
+          <t>why dbt is used in data engineering</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=why+dbt+is+used+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>workflow vs data pipeline</t>
+          <t>why power bi</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=workflow+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=why+power+bi</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>analytics engineering roundup</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+roundup</t>
+          <t>https://www.google.com/search?q=why+data+engineering+is+hard</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>analytics engineering course</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+is+hard</t>
+          <t>https://www.google.com/search?q=analytics+engineering+course</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>best data pipeline tools</t>
+          <t>best data pipeline architecture</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+tools</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>best data pipeline software for integration platforms</t>
+          <t>best data pipeline</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+software+for+integration+platforms</t>
+          <t>https://www.google.com/search?q=best+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>best data pipeline orchestration tools</t>
+          <t>best data engineering projects for resume</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+orchestration+tools</t>
+          <t>https://www.google.com/search?q=best+data+engineering+projects+for+resume</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>best data pipeline framework</t>
+          <t>best data engineering projects</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+framework</t>
+          <t>https://www.google.com/search?q=best+data+engineering+projects</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>best data pipeline for small business</t>
+          <t>accounting vs data analytics</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+for+small+business</t>
+          <t>https://www.google.com/search?q=accounting+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+the+future+of+everything</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+used+for</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+over+excel</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+stand+for</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>and data analytics</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+important</t>
+          <t>https://www.google.com/search?q=and+data+analytics</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>analytics engineering jobs</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+is+important</t>
+          <t>https://www.google.com/search?q=analytics+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>analytics engineering with sql and dbt pdf</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+course</t>
+          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt+pdf</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>analytics engineering with sql and dbt</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+as+a+career</t>
+          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>analytics engineering vs data science</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics</t>
+          <t>https://www.google.com/search?q=analytics+engineering+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>analytics engineering vs data engineering</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+used+for</t>
+          <t>https://www.google.com/search?q=analytics+engineering+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>analytics engineering salary</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+stand+for</t>
+          <t>https://www.google.com/search?q=analytics+engineering+salary</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>analytics engineering roundup</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+software</t>
+          <t>https://www.google.com/search?q=analytics+engineering+roundup</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>analytics engineering podcast</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+service</t>
+          <t>https://www.google.com/search?q=analytics+engineering+podcast</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>analytics engineering manager</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+report+builder</t>
+          <t>https://www.google.com/search?q=analytics+engineering+manager</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>analytics vs data engineering</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+a+good+career</t>
+          <t>https://www.google.com/search?q=analytics+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>data pipeline icon</t>
+          <t>data engineering system design</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+pipeline+icon</t>
+          <t>https://www.google.com/search?q=data+engineering+system+design</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>data analytics vs data science</t>
+          <t>data engineering things</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+vs+data+science</t>
+          <t>https://www.google.com/search?q=data+engineering+things</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+degree</t>
+          <t>https://www.google.com/search?q=data+engineering+vs+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>data pipeline architecture diagram</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+engineering</t>
+          <t>https://www.google.com/search?q=data+pipeline+architecture+diagram</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+in+accounting</t>
+          <t>https://www.google.com/search?q=data+pipeline+diagram</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>data pipeline icon</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+in+healthcare</t>
+          <t>https://www.google.com/search?q=data+pipeline+icon</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>data analytics vs data science</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+in+simple+words</t>
+          <t>https://www.google.com/search?q=data+analytics+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>data engineering academy</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+job</t>
+          <t>https://www.google.com/search?q=data+engineering+academy</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+salary</t>
+          <t>https://www.google.com/search?q=data+engineering+interview+questions</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>data engineering manager</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+used+for</t>
+          <t>https://www.google.com/search?q=data+engineering+manager</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+vs+data+science</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+salary</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>dbt vs act</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+act</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+skills</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>dbt vs airflow</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+airflow</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>dbt vs code extension</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+code+extension</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+all+about</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+development</t>
         </is>
       </c>
     </row>
@@ -7632,7 +7632,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>best dbt books</t>
+          <t>best data pipeline for small business</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+books</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+for+small+business</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+vs+data+science</t>
+          <t>https://www.google.com/search?q=database+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>dbt vs spark</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+skills</t>
+          <t>https://www.google.com/search?q=dbt+vs+spark</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>dbt vs snowflake</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+salary</t>
+          <t>https://www.google.com/search?q=dbt+vs+snowflake</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>dbt vs databricks</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+role</t>
+          <t>https://www.google.com/search?q=dbt+vs+databricks</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>dbt vs code extension</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+reddit</t>
+          <t>https://www.google.com/search?q=dbt+vs+code+extension</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>dbt vs airflow</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+in+simple+words</t>
+          <t>https://www.google.com/search?q=dbt+vs+airflow</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>accounting vs data analytics</t>
+          <t>dbt vs act</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=accounting+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=dbt+vs+act</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+and+analytics</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+ai</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dataops+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+orchestration</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline+fabric</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+management</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+sql</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=database+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+python</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>use of ai in analytics</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=use+of+ai+in+analytics</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+machine+learning</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=top+data+pipeline+solutions</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+etl</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+course</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+and+data+science</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+analytics</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=statistics+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+testing</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>best dbt books for therapists</t>
+          <t>data analytics apprenticeship google</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+books+for+therapists</t>
+          <t>https://www.google.com/search?q=data+analytics+apprenticeship+google</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>best analytics engineering course</t>
+          <t>data analytics apprenticeship</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+analytics+engineering+course</t>
+          <t>https://www.google.com/search?q=data+analytics+apprenticeship</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>best data analytics books</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+books</t>
+          <t>https://www.google.com/search?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>best data analytics bootcamp</t>
+          <t>cybersecurity vs data engineering</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+bootcamp</t>
+          <t>https://www.google.com/search?q=cybersecurity+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>best data analytics certification</t>
+          <t>cybersecurity vs data analytics</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+certification</t>
+          <t>https://www.google.com/search?q=cybersecurity+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>best data analytics certification reddit</t>
+          <t>what is power bi software</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+certification+reddit</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+software</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>best data analytics courses</t>
+          <t>best dbt therapist near me</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+courses</t>
+          <t>https://www.google.com/search?q=best+dbt+therapist+near+me</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>best power bi course for beginners</t>
+          <t>what is power bi service</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+course+for+beginners</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+service</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>best dbt training for therapists</t>
+          <t>best dbt podcast</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+training+for+therapists</t>
+          <t>https://www.google.com/search?q=best+dbt+podcast</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>best power bi books</t>
+          <t>best dbt books for therapists</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+books</t>
+          <t>https://www.google.com/search?q=best+dbt+books+for+therapists</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>best power bi certification</t>
+          <t>best dbt books</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+certification</t>
+          <t>https://www.google.com/search?q=best+dbt+books</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>data analytics google certification</t>
+          <t>best dbt apps</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+google+certification</t>
+          <t>https://www.google.com/search?q=best+dbt+apps</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>data analytics internships</t>
+          <t>best data pipeline tools</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+internships</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>best data pipeline software for integration platforms</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+salary</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+software+for+integration+platforms</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>business vs data analytics</t>
+          <t>best data pipeline orchestration tools</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=business+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+orchestration+tools</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>best data pipeline framework</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+pipeline+diagram</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+framework</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>data pipeline architecture diagram</t>
+          <t>best dbt skills</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+pipeline+architecture+diagram</t>
+          <t>https://www.google.com/search?q=best+dbt+skills</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>best dbt therapist near me</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+therapist+near+me</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+report+builder</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>best dbt skills</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+skills</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>best dbt podcast</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+podcast</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>what is power bi and tableau</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+vs+analytics+engineering</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+and+tableau</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>data engineering things</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+things</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+and+how+does+it+work</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>data engineering system design</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+system+design</t>
+          <t>https://www.google.com/search?q=what+is+llm+analytics</t>
         </is>
       </c>
     </row>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>best data engineering course reddit</t>
+          <t>what is dbt models</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+course+reddit</t>
+          <t>https://www.google.com/search?q=what+is+dbt+models</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>data engineering projects</t>
+          <t>data analytics internships</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+projects</t>
+          <t>https://www.google.com/search?q=data+analytics+internships</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>data engineering manager</t>
+          <t>what is dbt in snowflake</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+manager</t>
+          <t>https://www.google.com/search?q=what+is+dbt+in+snowflake</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>what is dbt fusion</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+interview+questions</t>
+          <t>https://www.google.com/search?q=what+is+dbt+fusion</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>data engineering academy</t>
+          <t>what is dbt data</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+academy</t>
+          <t>https://www.google.com/search?q=what+is+dbt+data</t>
         </is>
       </c>
     </row>
@@ -8920,7 +8920,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>best data engineering projects for resume</t>
+          <t>best power bi tutorial on youtube</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+projects+for+resume</t>
+          <t>https://www.google.com/search?q=best+power+bi+tutorial+on+youtube</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>best data engineering projects</t>
+          <t>best power bi training</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+projects</t>
+          <t>https://www.google.com/search?q=best+power+bi+training</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>best data engineering podcasts</t>
+          <t>best power bi dashboards</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+podcasts</t>
+          <t>https://www.google.com/search?q=best+power+bi+dashboards</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>best data engineering courses</t>
+          <t>best power bi courses</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+courses</t>
+          <t>https://www.google.com/search?q=best+power+bi+courses</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>data analytics apprenticeship google</t>
+          <t>data analytics salary</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+apprenticeship+google</t>
+          <t>https://www.google.com/search?q=data+analytics+salary</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>dbt mp</t>
+          <t>what is dbt labs</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9069,16 +9069,16 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>0.4178356713426854</v>
+        <v>0.5</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>suggest</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+mp</t>
+          <t>https://www.google.com/search?q=what+is+dbt+labs</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>dbt 2.0</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9097,16 +9097,16 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>0.3537785271271151</v>
+        <v>0.4478957915831664</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+2.0</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>power bi microsoft</t>
+          <t>dbt mp</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>0.2975951903807615</v>
+        <v>0.4178356713426854</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+mp</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>data and analytics</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9153,16 +9153,16 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>0.2975951903807615</v>
+        <v>0.3537643257130241</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+and+analytics</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>power bi microsoft</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>data and analytics</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9209,16 +9209,16 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>0.2828044398948235</v>
+        <v>0.2975951903807615</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://trends.google.com/trends/explore?q=data+and+analytics</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Apparently CodePen 2.0 sends data to their servers as you type</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9237,16 +9237,16 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0.2769230769230769</v>
+        <v>0.2975951903807615</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>https://news.ycombinator.com/item?id=49596976</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>The Dataflow Model Revisited</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9265,16 +9265,16 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>0.2744939271255061</v>
+        <v>0.2827930875298557</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>https://www.vldb.org/pvldb/volumes/19/paper/The%20Dataflow%20Model%20Revisited</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>software engineering</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9293,16 +9293,16 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>0.2214487866562293</v>
+        <v>0.2735470941883767</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=software+engineering</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9321,16 +9321,16 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>0.1803607214428858</v>
+        <v>0.2214398972362162</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>engineering data management</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0.1743486973947896</v>
+        <v>0.1803607214428858</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>ai data analytics</t>
+          <t>power bi que es y para que sirve</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>0.1623246492985972</v>
+        <v>0.1773547094188377</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=ai+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+que+es+y+para+que+sirve</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>engineering data management</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0.156312625250501</v>
+        <v>0.1743486973947896</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>power bi report</t>
+          <t>ai data analytics</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>0.1292585170340682</v>
+        <v>0.1623246492985972</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+report</t>
+          <t>https://trends.google.com/trends/explore?q=ai+data+analytics</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9461,16 +9461,16 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>0.1267738503843761</v>
+        <v>0.156312625250501</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>power bi report</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>0.1172344689378757</v>
+        <v>0.1292585170340682</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+report</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>business data analytics</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -9517,16 +9517,16 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>0.1142284569138277</v>
+        <v>0.1267687614154106</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=business+data+analytics</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>social engineering</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -9545,7 +9545,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>0.1142284569138277</v>
+        <v>0.1172344689378757</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>download power bi</t>
+          <t>business data analytics</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>0.1112224448897796</v>
+        <v>0.1142284569138277</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=business+data+analytics</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>social engineering</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>0.1112224448897796</v>
+        <v>0.1142284569138277</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=excel</t>
+          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>google data analytics</t>
+          <t>download power bi</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
         </is>
       </c>
     </row>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -9685,16 +9685,16 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>0.1110535717869974</v>
+        <v>0.1112224448897796</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://trends.google.com/trends/explore?q=excel</t>
         </is>
       </c>
     </row>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>google data analytics</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -9713,16 +9713,16 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>0.1099295477810562</v>
+        <v>0.1112224448897796</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>dbt pdf</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -9741,16 +9741,16 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>0.1082164328657315</v>
+        <v>0.1110491138630753</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+pdf</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>dashboard</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -9769,16 +9769,16 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>0.1022044088176353</v>
+        <v>0.1099251349778215</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dashboard</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Knap – Turn Data into Markdown</t>
+          <t>dbt pdf</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -9797,16 +9797,16 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>0.09959514170040486</v>
+        <v>0.1082164328657315</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>https://knap.md/</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+pdf</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>0.09823969811926697</v>
+        <v>0.098235754571182</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>power bi price</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>0.09619238476953906</v>
+        <v>0.09318637274549098</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+price</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>power bi free</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+free</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Revolut confirms customer data breach, falling for fake government requests</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9993,16 +9993,16 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>0.0874493927125506</v>
+        <v>0.08416833667334669</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/litigation/revolut-confirms-sensitive-customer-data-breach-falling-fake-government-requests-2026-09-12/</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>0.08416833667334669</v>
+        <v>0.0811623246492986</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10049,7 +10049,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>0.0811623246492986</v>
+        <v>0.07214428857715431</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Show HN: Filament – Fast data movement engine in Go</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10077,16 +10077,16 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>0.0728744939271255</v>
+        <v>0.06913827655310621</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>https://github.com/galaxy-io/filament</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10105,7 +10105,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>0.07214428857715431</v>
+        <v>0.06312625250501003</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>0.06913827655310621</v>
+        <v>0.06312625250501003</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10189,16 +10189,16 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>0.06312625250501003</v>
+        <v>0.06228448708427835</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>0.06312625250501003</v>
+        <v>0.06012024048096192</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10245,16 +10245,16 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>0.06228698741494551</v>
+        <v>0.06012024048096192</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>snowflake dbt</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10301,7 +10301,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>0.06012024048096192</v>
+        <v>0.05711422845691383</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+dbt</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>0.06012024048096192</v>
+        <v>0.05711422845691383</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10357,16 +10357,16 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>0.05711422845691383</v>
+        <v>0.05645585372217651</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>snowflake dbt</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10385,16 +10385,16 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>0.05711422845691383</v>
+        <v>0.05415972542801517</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+dbt</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>data engineering tools</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -10413,16 +10413,16 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>0.05645812006985006</v>
+        <v>0.05410821643286573</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+tools</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Apple wants to train AI on your private personal data</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -10441,16 +10441,16 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>0.05587044534412956</v>
+        <v>0.05244164341769866</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>https://machinelearning.apple.com/research/introducing-third-generation-of-apple-foundation-models</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>microsoft learn</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -10469,16 +10469,16 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>0.05416189960057004</v>
+        <v>0.05110220440881763</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+learn</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>OpenAI: "We use ... de-identified data to improve ChatGPT"</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -10497,16 +10497,16 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>0.0534412955465587</v>
+        <v>0.04919816149168055</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>https://twitter.com/markchen90/status/2097400166554993041</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -10525,16 +10525,16 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>0.05244374862005982</v>
+        <v>0.04809619238476953</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>microsoft learn</t>
+          <t>data analytics services</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -10553,7 +10553,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>0.05110220440881763</v>
+        <v>0.04809619238476953</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+learn</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+services</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Secret DHS Unit Pulling People over Based on Their Financial Data</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -10581,16 +10581,16 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>0.05101214574898785</v>
+        <v>0.04809619238476953</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>https://newrepublic.com/post/215177/secret-dhs-unit-predictive-policiing-people-based-financial-data</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>learn microsoft power bi</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -10609,16 +10609,16 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>0.0492001364886293</v>
+        <v>0.04809619238476953</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://trends.google.com/trends/explore?q=learn+microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -10628,7 +10628,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -10637,7 +10637,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.04509018036072144</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>data analytics software</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.04509018036072144</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+software</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>learn microsoft power bi</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -10693,16 +10693,16 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.04107339983541738</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+microsoft+power+bi</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>data analytics services</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.03907815631262525</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+services</t>
+          <t>https://trends.google.com/trends/explore?q=python</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>data analytics platform</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.03907815631262525</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+platform</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -10777,16 +10777,16 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>0.04509018036072144</v>
+        <v>0.03869698733516649</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>data analytics software</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10805,16 +10805,16 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>0.04509018036072144</v>
+        <v>0.03835979366959035</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+software</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>dbt training</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -10833,16 +10833,16 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>0.04107504867425383</v>
+        <v>0.03607214428857716</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+training</t>
         </is>
       </c>
     </row>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>power bi web</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>0.03907815631262525</v>
+        <v>0.03607214428857716</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>data analytics tools</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>0.03907815631262525</v>
+        <v>0.03006012024048096</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -10917,7 +10917,7 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>0.03869854077597801</v>
+        <v>0.02960881520582863</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>0.03836133357419563</v>
+        <v>0.02862934789153604</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>dbt training</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -10973,16 +10973,16 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>0.03607214428857716</v>
+        <v>0.02742508480019269</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+training</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>data analytics tools</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -11001,7 +11001,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>0.03006012024048096</v>
+        <v>0.02705410821643287</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>analytics engineer</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -11029,16 +11029,16 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>0.02961000381365288</v>
+        <v>0.02705410821643287</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://trends.google.com/trends/explore?q=analytics+engineer</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Massachusetts hits data centers with new clean power rules</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -11057,16 +11057,16 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>0.0291497975708502</v>
+        <v>0.02659012905686129</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/09/09/massachusetts-hits-data-centers-with-new-clean-power-rules/</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>0.02863049717990406</v>
+        <v>0.025193183870903</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>healthcare data analytics</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -11113,16 +11113,16 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>0.02742618574496698</v>
+        <v>0.02404809619238477</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://trends.google.com/trends/explore?q=healthcare+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>financial data analytics</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -11141,16 +11141,16 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0.02705410821643287</v>
+        <v>0.0214037693434759</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=financial+data+analytics</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -11169,16 +11169,16 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>0.02705410821643287</v>
+        <v>0.01994259679264597</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>LG accused of 'egregious invasion of privacy' over TV data collection</t>
+          <t>google data analytics certificate</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -11197,16 +11197,16 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>0.02672064777327935</v>
+        <v>0.01803607214428858</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/09/08/lg-accused-of-egregious-invasion-of-privacy-over-tv-data-collection/5294956</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certificate</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -11225,16 +11225,16 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>0.02659119648341061</v>
+        <v>0.01803607214428858</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -11253,16 +11253,16 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>0.0251941952188836</v>
+        <v>0.01503006012024048</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>data analytics healthcare</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -11281,7 +11281,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>0.02404809619238477</v>
+        <v>0.01202404809619238</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+healthcare</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -11300,7 +11300,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>big data and analytics</t>
+          <t>data analytics masters</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>0.02404809619238477</v>
+        <v>0.01202404809619238</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+and+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+masters</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Show HN: Forget Rigid Stock Screeners – A Universal Query API for Financial Data</t>
+          <t>data pipeline software</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -11337,16 +11337,16 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>0.02186234817813765</v>
+        <v>0.01202404809619238</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>https://financialdata.net/universal-query</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
         </is>
       </c>
     </row>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -11365,16 +11365,16 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>0.02140462857028161</v>
+        <v>0.01202404809619238</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>data analytics solutions</t>
+          <t>data analytics consulting</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>0.02104208416833667</v>
+        <v>0.01202404809619238</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+consulting</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -11421,7 +11421,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>0.01994339736255796</v>
+        <v>0.0112558456937559</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Show HN: Dbmask – Discover, mask, and verify sensitive data in SQL databases</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -11449,16 +11449,16 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>0.0194331983805668</v>
+        <v>0.01005158260241254</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>https://github.com/sealandseacat/dbmask</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>machine learning data analytics</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -11477,16 +11477,16 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>0.01803607214428858</v>
+        <v>0.009409308953696086</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=machine+learning+data+analytics</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>coursera</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>0.01803607214428858</v>
+        <v>0.009018036072144289</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=coursera</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>google data analytics certificate</t>
+          <t>data pipeline aws</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -11533,7 +11533,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>0.01803607214428858</v>
+        <v>0.009018036072144289</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certificate</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11561,16 +11561,16 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>0.01503006012024048</v>
+        <v>0.007337976436585513</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>data pipeline development</t>
+          <t>data pipeline solutions</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>0.01503006012024048</v>
+        <v>0.006012024048096191</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
         </is>
       </c>
     </row>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Show HN: I licensed $50k of stock market data to do analysis Claude can't</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -11617,16 +11617,16 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>0.0145748987854251</v>
+        <v>0.006012024048096191</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>https://www.athenic.com:443/</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Show HN: AI Brand Visibility for Free Forever</t>
+          <t>masters in data analytics</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -11645,16 +11645,16 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>0.0145748987854251</v>
+        <v>0.006012024048096191</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>https://app.geosurge.ai/login</t>
+          <t>https://trends.google.com/trends/explore?q=masters+in+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>data analytics consulting</t>
+          <t>etl data pipeline</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.006012024048096191</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>data analytics class</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -11701,16 +11701,16 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.005459326014089879</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+class</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>data pipeline software</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.003006012024048096</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>data engineering bootcamp</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -11757,7 +11757,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.003006012024048096</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+bootcamp</t>
         </is>
       </c>
     </row>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>google data analytics certification</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -11785,16 +11785,16 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>0.01125629754521186</v>
+        <v>0.003006012024048096</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>dbt in data engineering</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -11813,16 +11813,16 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>0.01005198611027478</v>
+        <v>0.003006012024048096</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Ada: An open-source data analyst that tells you when its own forecast is useless</t>
+          <t>data pipeline examples</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -11841,16 +11841,16 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>0.009716599190283401</v>
+        <v>0.003006012024048096</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>https://github.com/saineshnakra/automated-data-analyst</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+examples</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>what is big data analytics</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -11869,16 +11869,16 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>0.009409686678308344</v>
+        <v>0.003006012024048096</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11897,16 +11897,16 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>0.009018036072144289</v>
+        <v>0.002713606165827028</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>0.007338271010216575</v>
+        <v>0.002488810388776268</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -11953,16 +11953,16 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.002039218834674749</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>data pipeline solutions</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11981,16 +11981,16 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.001974991469803103</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12000,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>etl data pipeline</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -12009,16 +12009,16 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.001621740963009052</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>MUJTBA4F/attrition-insights-engineering</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>0.005459545171714739</v>
+        <v>0.001605684121791141</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://github.com/MUJTBA4F/attrition-insights-engineering</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>We rebuilt the old Google Analytics on top of GA4's data</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -12065,16 +12065,16 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>0.004858299595141701</v>
+        <v>0.001525399915701584</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>https://github.com/adacahq/adaca-analytics</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>An Analysis of Two Architectures for Agentic Data Analysis</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -12093,16 +12093,16 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>0.004858299595141701</v>
+        <v>0.00147722939204785</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>https://www.starburst.io/blog/an-analysis-of-two-architectures-for-agentic-data-analysis/</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -12112,7 +12112,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -12121,16 +12121,16 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.001268490456215001</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>data engineering bootcamp</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -12149,16 +12149,16 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.00125243361499709</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+bootcamp</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>data pipeline examples</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -12177,16 +12177,16 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.001188206250125444</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+examples</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>0.002713715100058208</v>
+        <v>0.001188206250125444</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>0.002488910298869955</v>
+        <v>0.001043694679164242</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Summation: AI Data Analyst</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -12261,16 +12261,16 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>0.00242914979757085</v>
+        <v>0.0009794673142925958</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>https://www.summation.com/</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>0.002039300696493447</v>
+        <v>0.0009152399494209503</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>0.001975070753296803</v>
+        <v>0.0007707283784597475</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>dataforgelabs/dataforge-core</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>0.001621806065715261</v>
+        <v>0.000706501013588102</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/dataforgelabs/dataforge-core</t>
         </is>
       </c>
     </row>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MUJTBA4F/attrition-insights-engineering</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -12373,7 +12373,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>0.0016057485799161</v>
+        <v>0.0005780462838448106</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>https://github.com/MUJTBA4F/attrition-insights-engineering</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>0.001525461150920295</v>
+        <v>0.0004495915541015194</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -12429,7 +12429,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>0.001477288693522812</v>
+        <v>0.000433534712883608</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
         </is>
       </c>
     </row>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>0.001268541378133719</v>
+        <v>0.0003693073480119624</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
         </is>
       </c>
     </row>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>Dreamerol/Dreamerol</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>0.001252483892334558</v>
+        <v>0.0003211368243582281</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>nirholas/bnbchain-mcp</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -12513,7 +12513,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>0.001188253949137914</v>
+        <v>0.0002569094594865825</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
         </is>
       </c>
     </row>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>Tony405-spec/feature-engineering-healthcare</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>0.001188253949137914</v>
+        <v>0.0001284547297432913</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://github.com/Tony405-spec/feature-engineering-healthcare</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>exmergo/dex</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>0.001043736576945465</v>
+        <v>0.0001123978885253799</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://github.com/exmergo/dex</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -12597,7 +12597,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>0.0009795066337488208</v>
+        <v>0.0001123978885253799</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
         </is>
       </c>
     </row>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>0.0009152766905521769</v>
+        <v>9.634104730746844e-05</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
         </is>
       </c>
     </row>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>A list of articles on how data teams built their analytics agents</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -12653,16 +12653,16 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>0.0007707593183597279</v>
+        <v>0</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://github.com/GetCassis/analytics-agent-articles</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>dataforgelabs/dataforge-core</t>
+          <t>Show HN: The Analyst (A data science analytics simulator)</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -12681,16 +12681,16 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>0.0007065293751630839</v>
+        <v>0</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>https://github.com/dataforgelabs/dataforge-core</t>
+          <t>https://theanalyst.dev</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>Designing a Dbt Pipeline for Consent Withdrawal</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -12709,16 +12709,16 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>0.0005780694887697959</v>
+        <v>0</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://kore-nordmann.de/blog/designing-a-dbt-pipeline-for-consent-withdrawal.html</t>
         </is>
       </c>
     </row>
@@ -12728,7 +12728,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>Dreamerol/ALLSTATS</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>0.000449609602376508</v>
+        <v>0</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>Assembling context for analytics agents from existing data stacks</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -12765,352 +12765,16 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>0.0004335521165773469</v>
+        <v>0</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="n">
-        <v>418</v>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D419" t="n">
-        <v>0.0003693221733807029</v>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="n">
-        <v>419</v>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Dreamerol/Dreamerol</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D420" t="n">
-        <v>0.0003211497159832199</v>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="n">
-        <v>420</v>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>nirholas/bnbchain-mcp</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D421" t="n">
-        <v>0.000256919772786576</v>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="n">
-        <v>421</v>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Tony405-spec/feature-engineering-healthcare</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D422" t="n">
-        <v>0.000128459886393288</v>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>https://github.com/Tony405-spec/feature-engineering-healthcare</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="n">
-        <v>422</v>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>exmergo/dex</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D423" t="n">
-        <v>0.000112402400594127</v>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>https://github.com/exmergo/dex</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="n">
-        <v>423</v>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D424" t="n">
-        <v>0.000112402400594127</v>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="n">
-        <v>424</v>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D425" t="n">
-        <v>9.634491479496599e-05</v>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="n">
-        <v>425</v>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Show HN: The Analyst (A data science analytics simulator)</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D426" t="n">
-        <v>0</v>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>hn</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>https://theanalyst.dev</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="n">
-        <v>426</v>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Designing a Dbt Pipeline for Consent Withdrawal</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D427" t="n">
-        <v>0</v>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>hn</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>https://kore-nordmann.de/blog/designing-a-dbt-pipeline-for-consent-withdrawal.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="n">
-        <v>427</v>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Dreamerol/ALLSTATS</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D428" t="n">
-        <v>0</v>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>github</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="n">
-        <v>428</v>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Assembling context for analytics agents from existing data stacks</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D429" t="n">
-        <v>0</v>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>hn</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
           <t>https://blog.getcassis.com/a-blank-beats-a-guess/</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="n">
-        <v>429</v>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>A list of articles on how data teams built their analytics agents</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D430" t="n">
-        <v>0</v>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>hn</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>https://github.com/GetCassis/analytics-agent-articles</t>
         </is>
       </c>
     </row>

--- a/reports/report_2026-09-13.xlsx
+++ b/reports/report_2026-09-13.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dbt biocare</t>
+          <t>google data analytics apprenticeship</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+biocare</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+apprenticeship</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.368987975951904</v>
+        <v>1.375</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.996993987975952</v>
+        <v>0.98875</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9443887775551102</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8654809619238477</v>
+        <v>0.9775</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8166332665330661</v>
+        <v>0.8875</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -661,16 +661,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>0.81625</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dbt data</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7715430861723447</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what is dbt</t>
+          <t>dbt data</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7565130260521041</v>
+        <v>0.79375</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
         </is>
       </c>
     </row>
@@ -810,12 +810,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "dbt biocare" (and what it should mean for your 2026 content plan)</t>
+          <t>Why everyone's suddenly talking about "google data analytics apprenticeship" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dbt biocare</t>
+          <t>google data analytics apprenticeship</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+biocare</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+apprenticeship</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.368987975951904</v>
+        <v>1.375</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -866,12 +866,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "data engineering" (and what it should mean for your 2026 content plan)</t>
+          <t>Why everyone's suddenly talking about "data analytics" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -880,11 +880,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.996993987975952</v>
+        <v>0.98875</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Data Engineering, explained in plain English (a 2026 beginner's guide)</t>
+          <t>Why everyone's suddenly talking about "data engineering" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -908,11 +908,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.9443887775551102</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "data engineering jobs" (and what it should mean for your 2026 content plan)</t>
+          <t>Data Engineering, explained in plain English (a 2026 beginner's guide)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -936,11 +936,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8654809619238477</v>
+        <v>0.9775</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "power bi desktop" (and what it should mean for your 2026 content plan)</t>
+          <t>Why everyone's suddenly talking about "data engineering jobs" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -964,11 +964,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8166332665330661</v>
+        <v>0.8875</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>I tried marketingskills so you don't have to — first impressions</t>
+          <t>Why everyone's suddenly talking about "power bi desktop" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -992,11 +992,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.8</v>
+        <v>0.81625</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Why everyone's suddenly talking about "dbt data" (and what it should mean for your 2026 content plan)</t>
+          <t>I tried marketingskills so you don't have to — first impressions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dbt data</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7715430861723447</v>
+        <v>0.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dbt, explained in plain English (a 2026 beginner's guide)</t>
+          <t>Why everyone's suddenly talking about "dbt data" (and what it should mean for your 2026 content plan)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>what is dbt</t>
+          <t>dbt data</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.7565130260521041</v>
+        <v>0.79375</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F418"/>
+  <dimension ref="A1:F432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dbt biocare</t>
+          <t>google data analytics apprenticeship</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+biocare</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+apprenticeship</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.368987975951904</v>
+        <v>1.375</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>data engineering</t>
+          <t>data analytics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.996993987975952</v>
+        <v>0.98875</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>what is data engineering</t>
+          <t>data engineering</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9443887775551102</v>
+        <v>0.9850000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>data engineering jobs</t>
+          <t>what is data engineering</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8654809619238477</v>
+        <v>0.9775</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+engineering</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>power bi desktop</t>
+          <t>data engineering jobs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8166332665330661</v>
+        <v>0.8875</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>coreyhaines31/marketingskills</t>
+          <t>power bi desktop</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8</v>
+        <v>0.81625</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://github.com/coreyhaines31/marketingskills</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dbt data</t>
+          <t>coreyhaines31/marketingskills</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7715430861723447</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
+          <t>https://github.com/coreyhaines31/marketingskills</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what is dbt</t>
+          <t>dbt data</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7565130260521041</v>
+        <v>0.79375</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>power bi dashboard</t>
+          <t>what is dbt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7565130260521041</v>
+        <v>0.77125</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+dashboard</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>what is power bi</t>
+          <t>power bi download</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.7527555110220441</v>
+        <v>0.7675</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+download</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>what is data analytics</t>
+          <t>what is power bi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.7339679358717435</v>
+        <v>0.76</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+power+bi</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DataTalksClub/data-engineering-zoomcamp</t>
+          <t>what is data analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1481,16 +1481,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.7301045701784317</v>
+        <v>0.74125</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+data+analytics</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dbt skills</t>
+          <t>power bi service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.7226953907815631</v>
+        <v>0.7374999999999999</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+skills</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dbt</t>
+          <t>DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1537,16 +1537,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.718937875751503</v>
+        <v>0.7301045701784317</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt</t>
+          <t>https://github.com/DataTalksClub/data-engineering-zoomcamp</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>data analytics jobs</t>
+          <t>dbt skills</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.7001503006012023</v>
+        <v>0.73</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+jobs</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+skills</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dbt meaning</t>
+          <t>data analytics jobs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.6813627254509018</v>
+        <v>0.7075</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+meaning</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+jobs</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>data engineering projects</t>
+          <t>dbt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.6776052104208418</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+projects</t>
+          <t>https://trends.google.com/trends/explore?q=dbt</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>data engineering courses</t>
+          <t>dbt meaning</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.6625751503006012</v>
+        <v>0.6887500000000001</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+meaning</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>data analytics courses</t>
+          <t>power bi training</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.658817635270541</v>
+        <v>0.6775</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+courses</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+training</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>what is a data pipeline</t>
+          <t>data engineering courses</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1705,16 +1705,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.6583166332665331</v>
+        <v>0.67</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>suggest, trends</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+a+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dbt labs</t>
+          <t>data analytics tools</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.655060120240481</v>
+        <v>0.66625</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+labs</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>data analytics degree</t>
+          <t>data analytics certification</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.6437875751503006</v>
+        <v>0.6475</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>data analytics certification</t>
+          <t>data pipeline architecture</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.6437875751503006</v>
+        <v>0.64375</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>data pipeline architecture</t>
+          <t>data pipeline tools</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.6400300601202404</v>
+        <v>0.64</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+architecture</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>data pipeline meaning</t>
+          <t>data pipeline examples</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.6400300601202404</v>
+        <v>0.6325000000000001</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+examples</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>data pipeline tools</t>
+          <t>what is dbt in data engineering</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.6362725450901803</v>
+        <v>0.62875</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+tools</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+dbt+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>data engineering zoomcamp</t>
+          <t>We rebuilt the old Google Analytics on top of GA4's data</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1901,16 +1901,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.6287575150300601</v>
+        <v>0.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>hn</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+zoomcamp</t>
+          <t>https://github.com/adacahq/adaca-analytics</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>what is dbt in data engineering</t>
+          <t>langfuse/langfuse</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1929,16 +1929,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.625</v>
+        <v>0.5539449651767256</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>suggest, trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+dbt+in+data+engineering</t>
+          <t>https://github.com/langfuse/langfuse</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>We rebuilt the old Google Analytics on top of GA4's data</t>
+          <t>what is a data pipeline</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1957,16 +1957,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.6</v>
+        <v>0.549</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://github.com/adacahq/adaca-analytics</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+a+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>langfuse/langfuse</t>
+          <t>excel vs power bi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1985,16 +1985,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.5539289083355077</v>
+        <v>0.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>suggest</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://github.com/langfuse/langfuse</t>
+          <t>https://www.google.com/search?q=excel+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>how to data engineering</t>
+          <t>exabeam ai agent analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+engineering</t>
+          <t>https://www.google.com/search?q=exabeam+ai+agent+analytics</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>how to data analytics work</t>
+          <t>how to design data pipeline</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+analytics+work</t>
+          <t>https://www.google.com/search?q=how+to+design+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>how to data analytics</t>
+          <t>fabric vs power bi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+analytics</t>
+          <t>https://www.google.com/search?q=fabric+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>how to create data pipeline in snowflake</t>
+          <t>dbt vs spark</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+snowflake</t>
+          <t>https://www.google.com/search?q=dbt+vs+spark</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>what is data analytics engineering</t>
+          <t>glue vs data pipeline</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+engineering</t>
+          <t>https://www.google.com/search?q=glue+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>how to create data pipeline in sql</t>
+          <t>dbt vs snowflake</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+sql</t>
+          <t>https://www.google.com/search?q=dbt+vs+snowflake</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>how to data pipeline</t>
+          <t>grafana vs power bi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+data+pipeline</t>
+          <t>https://www.google.com/search?q=grafana+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>how to dbt</t>
+          <t>dbt vs databricks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+dbt</t>
+          <t>https://www.google.com/search?q=dbt+vs+databricks</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>how to delete data analytics from iphone</t>
+          <t>dbt vs code extension</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+delete+data+analytics+from+iphone</t>
+          <t>https://www.google.com/search?q=dbt+vs+code+extension</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>how to design data pipeline</t>
+          <t>what is data analytics degree</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+design+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>visual studio data pipeline</t>
+          <t>how to power bi bas</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=visual+studio+data+pipeline</t>
+          <t>https://www.google.com/search?q=how+to+power+bi+bas</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>vs data analytics</t>
+          <t>how to power bi dashboard</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=vs+data+analytics</t>
+          <t>https://www.google.com/search?q=how+to+power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>vs dbt</t>
+          <t>how to power bi youtube</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=vs+dbt</t>
+          <t>https://www.google.com/search?q=how+to+power+bi+youtube</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>vs power bi</t>
+          <t>how to start data engineering</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=vs+power+bi</t>
+          <t>https://www.google.com/search?q=how+to+start+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>what is ai in analytics</t>
+          <t>how to study data analytics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+ai+in+analytics</t>
+          <t>https://www.google.com/search?q=how+to+study+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>how to learn data analytics for free</t>
+          <t>how to big data analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+data+analytics+for+free</t>
+          <t>https://www.google.com/search?q=how+to+big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>what is data analytics in accounting</t>
+          <t>how to create data pipeline in databricks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+in+accounting</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+databricks</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline fabric</t>
+          <t>how to create data pipeline in snowflake</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline+fabric</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+snowflake</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>dataops vs data engineering</t>
+          <t>how to create data pipeline in python</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dataops+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+python</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>what is data analytics in healthcare</t>
+          <t>what is data analytics and visualization</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+in+healthcare</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+and+visualization</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>what is data analytics in simple words</t>
+          <t>power bi vs tableau</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+in+simple+words</t>
+          <t>https://www.google.com/search?q=power+bi+vs+tableau</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>what is data analytics job</t>
+          <t>or power bi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+job</t>
+          <t>https://www.google.com/search?q=or+power+bi</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>what is data analytics salary</t>
+          <t>or power bi dax</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+salary</t>
+          <t>https://www.google.com/search?q=or+power+bi+dax</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>what is data analytics used for</t>
+          <t>or power bi measure</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+used+for</t>
+          <t>https://www.google.com/search?q=or+power+bi+measure</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>what is data analytics vs data science</t>
+          <t>or power bi symbol</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+vs+data+science</t>
+          <t>https://www.google.com/search?q=or+power+bi+symbol</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>what is data engineering all about</t>
+          <t>power bi</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+all+about</t>
+          <t>https://www.google.com/search?q=power+bi</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>what is data engineering and analytics</t>
+          <t>power bi certification</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+and+analytics</t>
+          <t>https://www.google.com/search?q=power+bi+certification</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>what is data engineering and data science</t>
+          <t>power bi dashboard</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+and+data+science</t>
+          <t>https://www.google.com/search?q=power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>what is data engineering course</t>
+          <t>power bi desktop download</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+course</t>
+          <t>https://www.google.com/search?q=power+bi+desktop+download</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>what is data engineering in simple words</t>
+          <t>what is data analytics engineering</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+in+simple+words</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>etl vs data pipeline</t>
+          <t>what is data analytics in accounting</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=etl+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+in+accounting</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>what is data engineering role</t>
+          <t>what is data analytics in healthcare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+role</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+in+healthcare</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>what is analytics engineering</t>
+          <t>devops vs data engineering</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+analytics+engineering</t>
+          <t>https://www.google.com/search?q=devops+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>what is analytics engineering dbt</t>
+          <t>what is data analytics job</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+analytics+engineering+dbt</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+job</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>what is analytics engineering reddit</t>
+          <t>what is data analytics salary</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+analytics+engineering+reddit</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+salary</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>what is data analytics and visualization</t>
+          <t>what is data analytics used for</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+and+visualization</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+used+for</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>what is data analytics degree</t>
+          <t>what is data analytics vs data science</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+analytics+degree</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>etl vs data engineering</t>
+          <t>data pipeline station</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=etl+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=data+pipeline+station</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>how to learn data engineering</t>
+          <t>what is data engineering all about</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+data+engineering</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+all+about</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>exabeam ai agent analytics</t>
+          <t>what is data engineering and analytics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=exabeam+ai+agent+analytics</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+and+analytics</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>excel vs power bi</t>
+          <t>dbt vs sqlmesh</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=excel+vs+power+bi</t>
+          <t>https://www.google.com/search?q=dbt+vs+sqlmesh</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>fabric vs power bi</t>
+          <t>what is data engineering and data science</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=fabric+vs+power+bi</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+and+data+science</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>glue vs data pipeline</t>
+          <t>what is data engineering course</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=glue+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>dbt vs sqlmesh</t>
+          <t>etl vs data engineering</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+sqlmesh</t>
+          <t>https://www.google.com/search?q=etl+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>devops vs data engineering</t>
+          <t>how to delete data analytics from iphone</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=devops+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+delete+data+analytics+from+iphone</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>what is data engineering reddit</t>
+          <t>what is data analytics in simple words</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+reddit</t>
+          <t>https://www.google.com/search?q=what+is+data+analytics+in+simple+words</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>workflow vs data pipeline</t>
+          <t>what is power bi software</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=workflow+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+software</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>why power bi over tableau</t>
+          <t>what is power bi service</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+over+tableau</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+service</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>why power bi over excel</t>
+          <t>best analytics engineering course</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+over+excel</t>
+          <t>https://www.google.com/search?q=best+analytics+engineering+course</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>why power bi is used</t>
+          <t>best analytics engineering books</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+used</t>
+          <t>https://www.google.com/search?q=best+analytics+engineering+books</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>why power bi is not available for mac</t>
+          <t>best ai agent analytics tools</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+not+available+for+mac</t>
+          <t>https://www.google.com/search?q=best+ai+agent+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>why power bi is important</t>
+          <t>backend vs data engineering</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+important</t>
+          <t>https://www.google.com/search?q=backend+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>why power bi is better than tableau</t>
+          <t>api vs data pipeline</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+better+than+tableau</t>
+          <t>https://www.google.com/search?q=api+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>why power bi is better than excel</t>
+          <t>and data analytics</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+is+better+than+excel</t>
+          <t>https://www.google.com/search?q=and+data+analytics</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>how to master data engineering</t>
+          <t>how to data analytics work</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+master+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+data+analytics+work</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>why data analytics</t>
+          <t>ai in analytics</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics</t>
+          <t>https://www.google.com/search?q=ai+in+analytics</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>top data pipeline solutions</t>
+          <t>why power bi is used</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=top+data+pipeline+solutions</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+used</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>tableau vs power bi</t>
+          <t>ai in analytics course</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=tableau+vs+power+bi</t>
+          <t>https://www.google.com/search?q=ai+in+analytics+course</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>statistics vs data analytics</t>
+          <t>use of ai in analytics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=statistics+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=use+of+ai+in+analytics</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>software vs data engineering</t>
+          <t>top data pipeline solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=software+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=top+data+pipeline+solutions</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>or power bi symbol</t>
+          <t>mlops vs data engineering</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi+symbol</t>
+          <t>https://www.google.com/search?q=mlops+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>or power bi measure</t>
+          <t>looker vs power bi</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi+measure</t>
+          <t>https://www.google.com/search?q=looker+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>or power bi dax</t>
+          <t>llm analytics vidhya</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi+dax</t>
+          <t>https://www.google.com/search?q=llm+analytics+vidhya</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>why power bi gateway went offline</t>
+          <t>analytics vs data engineering</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+power+bi+gateway+went+offline</t>
+          <t>https://www.google.com/search?q=analytics+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>why data engineering interview questions</t>
+          <t>analytics engineering vs data science</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+interview+questions</t>
+          <t>https://www.google.com/search?q=analytics+engineering+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>why dbt app is not working</t>
+          <t>analytics engineering vs data engineering</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt+app+is+not+working</t>
+          <t>https://www.google.com/search?q=analytics+engineering+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>why dbt</t>
+          <t>analytics engineering salary</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt</t>
+          <t>https://www.google.com/search?q=analytics+engineering+salary</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>why data pipeline</t>
+          <t>analytics engineering roundup</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+pipeline</t>
+          <t>https://www.google.com/search?q=analytics+engineering+roundup</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ai vs data engineering</t>
+          <t>analytics engineering podcast</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=analytics+engineering+podcast</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ai vs data analytics</t>
+          <t>analytics engineering manager</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=analytics+engineering+manager</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ai in analytics course</t>
+          <t>analytics engineering jobs</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+in+analytics+course</t>
+          <t>https://www.google.com/search?q=analytics+engineering+jobs</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ai in analytics</t>
+          <t>analytics engineering course</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+in+analytics</t>
+          <t>https://www.google.com/search?q=analytics+engineering+course</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>what is power bi stand for</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+stand+for</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ai agent analytics servicenow</t>
+          <t>analytics engineering</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+servicenow</t>
+          <t>https://www.google.com/search?q=analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ai agent analytics platform</t>
+          <t>ai vs data engineering</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+platform</t>
+          <t>https://www.google.com/search?q=ai+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ai agent analytics dashboard servicenow</t>
+          <t>ai vs data analytics</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard+servicenow</t>
+          <t>https://www.google.com/search?q=ai+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ai agent analytics dashboard</t>
+          <t>why power bi over tableau</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard</t>
+          <t>https://www.google.com/search?q=why+power+bi+over+tableau</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ai agent analytics</t>
+          <t>vs data analytics</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics</t>
+          <t>https://www.google.com/search?q=vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>why data engineering reddit</t>
+          <t>why data engineering is important</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+reddit</t>
+          <t>https://www.google.com/search?q=why+data+engineering+is+important</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>why data engineering is important</t>
+          <t>why data engineering reddit</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+is+important</t>
+          <t>https://www.google.com/search?q=why+data+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>power bi courses</t>
+          <t>why data analytics</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+courses</t>
+          <t>https://www.google.com/search?q=why+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>power bi certification</t>
+          <t>what is power bi used for</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+certification</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+used+for</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ai agent analytics vidhya</t>
+          <t>analytics engineering best practices</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=ai+agent+analytics+vidhya</t>
+          <t>https://www.google.com/search?q=analytics+engineering+best+practices</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>llm analytics</t>
+          <t>how to learn data engineering</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics</t>
+          <t>https://www.google.com/search?q=how+to+learn+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>integration vs data pipeline</t>
+          <t>how to learn data analytics for free</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=integration+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=how+to+learn+data+analytics+for+free</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>use of ai in analytics</t>
+          <t>how to learn data analytics</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=use+of+ai+in+analytics</t>
+          <t>https://www.google.com/search?q=how+to+learn+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>how to create data pipeline in python</t>
+          <t>how to learn analytics engineering</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+python</t>
+          <t>https://www.google.com/search?q=how+to+learn+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>how to create data pipeline in databricks</t>
+          <t>how to get into data engineering</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+databricks</t>
+          <t>https://www.google.com/search?q=how+to+get+into+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>how to big data analytics</t>
+          <t>how to do data analytics</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+big+data+analytics</t>
+          <t>https://www.google.com/search?q=how+to+do+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>grafana vs power bi</t>
+          <t>llm analytics tools</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=grafana+vs+power+bi</t>
+          <t>https://www.google.com/search?q=llm+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>how to study data analytics</t>
+          <t>llm analytics posthog</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+study+data+analytics</t>
+          <t>https://www.google.com/search?q=llm+analytics+posthog</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>or power bi</t>
+          <t>tableau vs power bi</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=or+power+bi</t>
+          <t>https://www.google.com/search?q=tableau+vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>how to power bi youtube</t>
+          <t>llm analytics meaning</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi+youtube</t>
+          <t>https://www.google.com/search?q=llm+analytics+meaning</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>how to power bi dashboard</t>
+          <t>llm analytics leaderboard</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi+dashboard</t>
+          <t>https://www.google.com/search?q=llm+analytics+leaderboard</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>how to power bi bas</t>
+          <t>how to dbt</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi+bas</t>
+          <t>https://www.google.com/search?q=how+to+dbt</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>how to power bi</t>
+          <t>how to data pipeline</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+power+bi</t>
+          <t>https://www.google.com/search?q=how+to+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>how to optimize data pipeline</t>
+          <t>how to data engineering</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+optimize+data+pipeline</t>
+          <t>https://www.google.com/search?q=how+to+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>dataflow vs data pipeline</t>
+          <t>dbt vs airflow</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=dbt+vs+airflow</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>how to master data analytics</t>
+          <t>how to data analytics</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+master+data+analytics</t>
+          <t>https://www.google.com/search?q=how+to+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>how to learn python for data engineering</t>
+          <t>how to create data pipeline in sql</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+python+for+data+engineering</t>
+          <t>https://www.google.com/search?q=how+to+create+data+pipeline+in+sql</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>how to start data engineering</t>
+          <t>llm analytics platform</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+start+data+engineering</t>
+          <t>https://www.google.com/search?q=llm+analytics+platform</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>mlops vs data engineering</t>
+          <t>statistics vs data analytics</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=mlops+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=statistics+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>looker vs power bi</t>
+          <t>software vs data engineering</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=looker+vs+power+bi</t>
+          <t>https://www.google.com/search?q=software+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>llm analytics vidhya</t>
+          <t>power bi login</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+vidhya</t>
+          <t>https://www.google.com/search?q=power+bi+login</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>power bi vs tableau</t>
+          <t>llm analytics dashboard</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+vs+tableau</t>
+          <t>https://www.google.com/search?q=llm+analytics+dashboard</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>power bi training</t>
+          <t>llm analytics comparison</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+training</t>
+          <t>https://www.google.com/search?q=llm+analytics+comparison</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>power bi login</t>
+          <t>llm analytics benchmark</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+login</t>
+          <t>https://www.google.com/search?q=llm+analytics+benchmark</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>power bi download</t>
+          <t>llm analytics</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+download</t>
+          <t>https://www.google.com/search?q=llm+analytics</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>how to learn data analytics</t>
+          <t>integration vs data pipeline</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+data+analytics</t>
+          <t>https://www.google.com/search?q=integration+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>llm analytics benchmark</t>
+          <t>how to learn python for data engineering</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+benchmark</t>
+          <t>https://www.google.com/search?q=how+to+learn+python+for+data+engineering</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>how to get into data engineering</t>
+          <t>what is analytics engineering dbt</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+get+into+data+engineering</t>
+          <t>https://www.google.com/search?q=what+is+analytics+engineering+dbt</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>how to do data analytics</t>
+          <t>what is analytics engineering</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+do+data+analytics</t>
+          <t>https://www.google.com/search?q=what+is+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>llm analytics tools</t>
+          <t>what is ai in analytics</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+tools</t>
+          <t>https://www.google.com/search?q=what+is+ai+in+analytics</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>llm analytics posthog</t>
+          <t>vs power bi</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+posthog</t>
+          <t>https://www.google.com/search?q=vs+power+bi</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>llm analytics platform</t>
+          <t>vs dbt</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+platform</t>
+          <t>https://www.google.com/search?q=vs+dbt</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>llm analytics meaning</t>
+          <t>how to power bi</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+meaning</t>
+          <t>https://www.google.com/search?q=how+to+power+bi</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>llm analytics leaderboard</t>
+          <t>how to optimize data pipeline</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+leaderboard</t>
+          <t>https://www.google.com/search?q=how+to+optimize+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>llm analytics dashboard</t>
+          <t>how to master data engineering</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+dashboard</t>
+          <t>https://www.google.com/search?q=how+to+master+data+engineering</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>llm analytics comparison</t>
+          <t>how to master data analytics</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=llm+analytics+comparison</t>
+          <t>https://www.google.com/search?q=how+to+master+data+analytics</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>how to learn analytics engineering</t>
+          <t>what is analytics engineering reddit</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=how+to+learn+analytics+engineering</t>
+          <t>https://www.google.com/search?q=what+is+analytics+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>api vs data pipeline</t>
+          <t>best data analytics certification reddit</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=api+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=best+data+analytics+certification+reddit</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>backend vs data engineering</t>
+          <t>best data analytics courses</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=backend+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=best+data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>best ai agent analytics tools</t>
+          <t>best data analytics courses reddit</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+ai+agent+analytics+tools</t>
+          <t>https://www.google.com/search?q=best+data+analytics+courses+reddit</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>best analytics engineering books</t>
+          <t>best data analytics masters programs</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+analytics+engineering+books</t>
+          <t>https://www.google.com/search?q=best+data+analytics+masters+programs</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>best analytics engineering course</t>
+          <t>best data analytics programs</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+analytics+engineering+course</t>
+          <t>https://www.google.com/search?q=best+data+analytics+programs</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>best data analytics books</t>
+          <t>best data analytics software</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+books</t>
+          <t>https://www.google.com/search?q=best+data+analytics+software</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>best data analytics bootcamp</t>
+          <t>best data analytics tools</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+bootcamp</t>
+          <t>https://www.google.com/search?q=best+data+analytics+tools</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>best data analytics certification</t>
+          <t>best data engineering blogs</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+certification</t>
+          <t>https://www.google.com/search?q=best+data+engineering+blogs</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>best data analytics certification reddit</t>
+          <t>best data engineering books</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+certification+reddit</t>
+          <t>https://www.google.com/search?q=best+data+engineering+books</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>best data analytics courses</t>
+          <t>best data engineering bootcamp</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+courses</t>
+          <t>https://www.google.com/search?q=best+data+engineering+bootcamp</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>best data analytics courses reddit</t>
+          <t>best data engineering certifications</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+courses+reddit</t>
+          <t>https://www.google.com/search?q=best+data+engineering+certifications</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>analytics engineering</t>
+          <t>best data engineering certifications 2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering</t>
+          <t>https://www.google.com/search?q=best+data+engineering+certifications+2026</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>best dbt training for therapists</t>
+          <t>best data engineering course reddit</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+training+for+therapists</t>
+          <t>https://www.google.com/search?q=best+data+engineering+course+reddit</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>best power bi books</t>
+          <t>analytics engineering with sql and dbt pdf</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+books</t>
+          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt+pdf</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>best power bi certification</t>
+          <t>best data engineering podcasts</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+certification</t>
+          <t>https://www.google.com/search?q=best+data+engineering+podcasts</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>why dbt is used</t>
+          <t>what is data engineering reddit</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt+is+used</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>best data pipeline development services</t>
+          <t>best dbt therapist near me</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+development+services</t>
+          <t>https://www.google.com/search?q=best+dbt+therapist+near+me</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>cloud vs data engineering</t>
+          <t>best dbt skills</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=cloud+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=best+dbt+skills</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>business vs data analytics</t>
+          <t>best data analytics books</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=business+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=best+data+analytics+books</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>best power bi visuals</t>
+          <t>best dbt podcast</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+visuals</t>
+          <t>https://www.google.com/search?q=best+dbt+podcast</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>best data engineering podcasts</t>
+          <t>best dbt books for therapists</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+podcasts</t>
+          <t>https://www.google.com/search?q=best+dbt+books+for+therapists</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>best data engineering courses</t>
+          <t>best dbt books</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+courses</t>
+          <t>https://www.google.com/search?q=best+dbt+books</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>best data engineering course reddit</t>
+          <t>best dbt apps</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+course+reddit</t>
+          <t>https://www.google.com/search?q=best+dbt+apps</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>best power bi course for beginners</t>
+          <t>best data engineering projects</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+course+for+beginners</t>
+          <t>https://www.google.com/search?q=best+data+engineering+projects</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>best data engineering certifications</t>
+          <t>best data pipeline software for integration platforms</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+certifications</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+software+for+integration+platforms</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>best data engineering bootcamp</t>
+          <t>best data pipeline orchestration tools</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+bootcamp</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+orchestration+tools</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>best data engineering books</t>
+          <t>best data pipeline framework</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+books</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+framework</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>best data engineering blogs</t>
+          <t>best data pipeline for small business</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+blogs</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+for+small+business</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>best data analytics tools</t>
+          <t>best data pipeline development services</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+tools</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+development+services</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>best data analytics software</t>
+          <t>best data pipeline architecture</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+software</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>best data analytics programs</t>
+          <t>best data pipeline</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+programs</t>
+          <t>https://www.google.com/search?q=best+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>best data analytics masters programs</t>
+          <t>best data engineering projects for resume</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+analytics+masters+programs</t>
+          <t>https://www.google.com/search?q=best+data+engineering+projects+for+resume</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>best data engineering certifications 2026</t>
+          <t>best data pipeline tools</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+certifications+2026</t>
+          <t>https://www.google.com/search?q=best+data+pipeline+tools</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>why data engineering</t>
+          <t>why data analytics is important</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+important</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>why data analytics reddit</t>
+          <t>why data pipeline</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+reddit</t>
+          <t>https://www.google.com/search?q=why+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>why data analytics is used</t>
+          <t>accounting vs data analytics</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+used</t>
+          <t>https://www.google.com/search?q=accounting+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>why data analytics is the future of everything</t>
+          <t>why power bi is not available for mac</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+the+future+of+everything</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+not+available+for+mac</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>why data analytics is the future</t>
+          <t>analytics engineering with sql and dbt</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+the+future</t>
+          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>why data analytics is important</t>
+          <t>why data engineering is hard</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+important</t>
+          <t>https://www.google.com/search?q=why+data+engineering+is+hard</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>why data analytics is a good career</t>
+          <t>why data analytics as a career</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+is+a+good+career</t>
+          <t>https://www.google.com/search?q=why+data+analytics+as+a+career</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>why data analytics course</t>
+          <t>best data analytics certification</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+course</t>
+          <t>https://www.google.com/search?q=best+data+analytics+certification</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>why data analytics as a career</t>
+          <t>why power bi is important</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+analytics+as+a+career</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+important</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>power bi desktop download</t>
+          <t>why power bi is better than tableau</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=power+bi+desktop+download</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+better+than+tableau</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>analytics engineering best practices</t>
+          <t>why power bi is better than excel</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+best+practices</t>
+          <t>https://www.google.com/search?q=why+power+bi+is+better+than+excel</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>why dbt is used in data engineering</t>
+          <t>why power bi gateway went offline</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+dbt+is+used+in+data+engineering</t>
+          <t>https://www.google.com/search?q=why+power+bi+gateway+went+offline</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>why data engineering is hard</t>
+          <t>why dbt is used in data engineering</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=why+data+engineering+is+hard</t>
+          <t>https://www.google.com/search?q=why+dbt+is+used+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>analytics engineering course</t>
+          <t>why dbt is used</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+course</t>
+          <t>https://www.google.com/search?q=why+dbt+is+used</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>best data pipeline architecture</t>
+          <t>why dbt app is not working</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+architecture</t>
+          <t>https://www.google.com/search?q=why+dbt+app+is+not+working</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>best data pipeline</t>
+          <t>visual studio data pipeline</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline</t>
+          <t>https://www.google.com/search?q=visual+studio+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>best data engineering projects for resume</t>
+          <t>best data analytics bootcamp</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+projects+for+resume</t>
+          <t>https://www.google.com/search?q=best+data+analytics+bootcamp</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>best data engineering projects</t>
+          <t>why data analytics is a good career</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+engineering+projects</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+a+good+career</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>accounting vs data analytics</t>
+          <t>why data analytics course</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=accounting+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=why+data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>what is power bi used for</t>
+          <t>workflow vs data pipeline</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+used+for</t>
+          <t>https://www.google.com/search?q=workflow+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>what is power bi stand for</t>
+          <t>why power bi over excel</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+stand+for</t>
+          <t>https://www.google.com/search?q=why+power+bi+over+excel</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>and data analytics</t>
+          <t>ai agent analytics</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=and+data+analytics</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>analytics engineering jobs</t>
+          <t>ai agent analytics dashboard</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+jobs</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>analytics engineering with sql and dbt pdf</t>
+          <t>why data analytics is the future</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt+pdf</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+the+future</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>analytics engineering with sql and dbt</t>
+          <t>ai agent analytics platform</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+with+sql+and+dbt</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+platform</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>analytics engineering vs data science</t>
+          <t>ai agent analytics servicenow</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+vs+data+science</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+servicenow</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>analytics engineering vs data engineering</t>
+          <t>ai agent analytics vidhya</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+vidhya</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>analytics engineering salary</t>
+          <t>why data engineering interview questions</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+salary</t>
+          <t>https://www.google.com/search?q=why+data+engineering+interview+questions</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>analytics engineering roundup</t>
+          <t>why data engineering</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+roundup</t>
+          <t>https://www.google.com/search?q=why+data+engineering</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>analytics engineering podcast</t>
+          <t>why data analytics reddit</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+podcast</t>
+          <t>https://www.google.com/search?q=why+data+analytics+reddit</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>analytics engineering manager</t>
+          <t>why data analytics is used</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+engineering+manager</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+used</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>analytics vs data engineering</t>
+          <t>why data analytics is the future of everything</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=analytics+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=why+data+analytics+is+the+future+of+everything</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>data engineering system design</t>
+          <t>ai agent analytics dashboard servicenow</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+system+design</t>
+          <t>https://www.google.com/search?q=ai+agent+analytics+dashboard+servicenow</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>data engineering things</t>
+          <t>data engineering certification</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+things</t>
+          <t>https://www.google.com/search?q=data+engineering+certification</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>data engineering vs analytics engineering</t>
+          <t>data engineering internship</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+vs+analytics+engineering</t>
+          <t>https://www.google.com/search?q=data+engineering+internship</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>data pipeline architecture diagram</t>
+          <t>data engineering interview questions</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+pipeline+architecture+diagram</t>
+          <t>https://www.google.com/search?q=data+engineering+interview+questions</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>data pipeline diagram</t>
+          <t>data engineering reddit</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+pipeline+diagram</t>
+          <t>https://www.google.com/search?q=data+engineering+reddit</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>data pipeline icon</t>
+          <t>data engineering salary</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+pipeline+icon</t>
+          <t>https://www.google.com/search?q=data+engineering+salary</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>data analytics vs data science</t>
+          <t>data analytics courses</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+vs+data+science</t>
+          <t>https://www.google.com/search?q=data+analytics+courses</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>data engineering academy</t>
+          <t>what is data pipeline architecture</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+academy</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+architecture</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>data engineering interview questions</t>
+          <t>what is data pipeline development</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+interview+questions</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+development</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>data engineering manager</t>
+          <t>what is data pipeline in ai</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+engineering+manager</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+ai</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>what is data engineering salary</t>
+          <t>what is data pipeline in data analytics</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+salary</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+analytics</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>what is data engineering skills</t>
+          <t>what is data pipeline in data engineering</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+skills</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+engineering</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>what is data engineering vs data science</t>
+          <t>what is data pipeline in etl</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+engineering+vs+data+science</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+etl</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>what is data pipeline architecture</t>
+          <t>what is data pipeline in machine learning</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+architecture</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+machine+learning</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>what is data pipeline development</t>
+          <t>what is data pipeline in python</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+development</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+python</t>
         </is>
       </c>
     </row>
@@ -7632,7 +7632,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>best data pipeline for small business</t>
+          <t>what is data pipeline in sql</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+for+small+business</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+in+sql</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>database vs data pipeline</t>
+          <t>best dbt training for therapists</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=database+vs+data+pipeline</t>
+          <t>https://www.google.com/search?q=best+dbt+training+for+therapists</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>dbt vs spark</t>
+          <t>dbt vs act</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+spark</t>
+          <t>https://www.google.com/search?q=dbt+vs+act</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>dbt vs snowflake</t>
+          <t>etl vs data pipeline</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+snowflake</t>
+          <t>https://www.google.com/search?q=etl+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>dbt vs databricks</t>
+          <t>what is data engineering vs data science</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+databricks</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>dbt vs code extension</t>
+          <t>what is data engineering skills</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+code+extension</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+skills</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7800,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>dbt vs airflow</t>
+          <t>what is data engineering salary</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+airflow</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+salary</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>dbt vs act</t>
+          <t>what is data engineering role</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=dbt+vs+act</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+role</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>what is data pipeline in ai</t>
+          <t>why dbt</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+ai</t>
+          <t>https://www.google.com/search?q=why+dbt</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>what is data pipeline orchestration</t>
+          <t>data engineering vs analytics engineering</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+orchestration</t>
+          <t>https://www.google.com/search?q=data+engineering+vs+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>what is data pipeline management</t>
+          <t>dataops vs data engineering</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+management</t>
+          <t>https://www.google.com/search?q=dataops+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>what is data pipeline in sql</t>
+          <t>dataflow vs data pipeline fabric</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+sql</t>
+          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline+fabric</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>what is data pipeline in python</t>
+          <t>dataflow vs data pipeline</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+python</t>
+          <t>https://www.google.com/search?q=dataflow+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>what is data pipeline in machine learning</t>
+          <t>database vs data pipeline</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+machine+learning</t>
+          <t>https://www.google.com/search?q=database+vs+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>what is data pipeline in etl</t>
+          <t>data pipeline engineer</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+etl</t>
+          <t>https://www.google.com/search?q=data+pipeline+engineer</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>what is data pipeline in data engineering</t>
+          <t>data pipeline diagram</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+engineering</t>
+          <t>https://www.google.com/search?q=data+pipeline+diagram</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>what is data pipeline in data analytics</t>
+          <t>data pipeline</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+in+data+analytics</t>
+          <t>https://www.google.com/search?q=data+pipeline</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>what is data pipeline testing</t>
+          <t>data engineering vs data science</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+data+pipeline+testing</t>
+          <t>https://www.google.com/search?q=data+engineering+vs+data+science</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>data analytics apprenticeship google</t>
+          <t>what is data engineering in simple words</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+apprenticeship+google</t>
+          <t>https://www.google.com/search?q=what+is+data+engineering+in+simple+words</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>data analytics apprenticeship</t>
+          <t>what is power bi report builder</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+apprenticeship</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+report+builder</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>data analytics</t>
+          <t>what is power bi pro</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>cybersecurity vs data engineering</t>
+          <t>what is power bi desktop</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=cybersecurity+vs+data+engineering</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+desktop</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>cybersecurity vs data analytics</t>
+          <t>what is power bi dashboard</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=cybersecurity+vs+data+analytics</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+dashboard</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>what is power bi software</t>
+          <t>what is power bi and how does it work</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+software</t>
+          <t>https://www.google.com/search?q=what+is+power+bi+and+how+does+it+work</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>best dbt therapist near me</t>
+          <t>what is llm analytics</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+therapist+near+me</t>
+          <t>https://www.google.com/search?q=what+is+llm+analytics</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>what is power bi service</t>
+          <t>what is dbt used for</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+service</t>
+          <t>https://www.google.com/search?q=what+is+dbt+used+for</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>best dbt podcast</t>
+          <t>data engineering academy</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+podcast</t>
+          <t>https://www.google.com/search?q=data+engineering+academy</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>best dbt books for therapists</t>
+          <t>best power bi visuals</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+books+for+therapists</t>
+          <t>https://www.google.com/search?q=best+power+bi+visuals</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>best dbt books</t>
+          <t>best power bi tutorial on youtube</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+books</t>
+          <t>https://www.google.com/search?q=best+power+bi+tutorial+on+youtube</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>best dbt apps</t>
+          <t>best power bi training</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+apps</t>
+          <t>https://www.google.com/search?q=best+power+bi+training</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>best data pipeline tools</t>
+          <t>best power bi dashboards</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+tools</t>
+          <t>https://www.google.com/search?q=best+power+bi+dashboards</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>best data pipeline software for integration platforms</t>
+          <t>best power bi courses</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+software+for+integration+platforms</t>
+          <t>https://www.google.com/search?q=best+power+bi+courses</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>best data pipeline orchestration tools</t>
+          <t>best power bi course for beginners</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+orchestration+tools</t>
+          <t>https://www.google.com/search?q=best+power+bi+course+for+beginners</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>best data pipeline framework</t>
+          <t>best power bi certification</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+data+pipeline+framework</t>
+          <t>https://www.google.com/search?q=best+power+bi+certification</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>best dbt skills</t>
+          <t>best power bi books</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+dbt+skills</t>
+          <t>https://www.google.com/search?q=best+power+bi+books</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>what is power bi report builder</t>
+          <t>best data engineering courses</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+report+builder</t>
+          <t>https://www.google.com/search?q=best+data+engineering+courses</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>what is power bi pro</t>
+          <t>data pipeline orchestration</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+pro</t>
+          <t>https://www.google.com/search?q=data+pipeline+orchestration</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>what is power bi desktop</t>
+          <t>data pipeline icon</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+desktop</t>
+          <t>https://www.google.com/search?q=data+pipeline+icon</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>what is power bi and tableau</t>
+          <t>what is dbt treatment</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+and+tableau</t>
+          <t>https://www.google.com/search?q=what+is+dbt+treatment</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>what is power bi and how does it work</t>
+          <t>what is dbt labs</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+power+bi+and+how+does+it+work</t>
+          <t>https://www.google.com/search?q=what+is+dbt+labs</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>what is llm analytics</t>
+          <t>what is dbt data</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+llm+analytics</t>
+          <t>https://www.google.com/search?q=what+is+dbt+data</t>
         </is>
       </c>
     </row>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>what is dbt models</t>
+          <t>what is data pipeline testing</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+models</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+testing</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>data analytics internships</t>
+          <t>what is data pipeline orchestration</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+internships</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+orchestration</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>what is dbt in snowflake</t>
+          <t>business vs data analytics</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+in+snowflake</t>
+          <t>https://www.google.com/search?q=business+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>what is dbt fusion</t>
+          <t>data analytics salary</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+fusion</t>
+          <t>https://www.google.com/search?q=data+analytics+salary</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>what is dbt data</t>
+          <t>data analytics professional certificate</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+data</t>
+          <t>https://www.google.com/search?q=data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -8920,7 +8920,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>best power bi tutorial on youtube</t>
+          <t>data analytics masters</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+tutorial+on+youtube</t>
+          <t>https://www.google.com/search?q=data+analytics+masters</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>best power bi training</t>
+          <t>data analytics jobs entry level</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+training</t>
+          <t>https://www.google.com/search?q=data+analytics+jobs+entry+level</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>best power bi dashboards</t>
+          <t>data analytics internships</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+dashboards</t>
+          <t>https://www.google.com/search?q=data+analytics+internships</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>best power bi courses</t>
+          <t>cybersecurity vs data engineering</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=best+power+bi+courses</t>
+          <t>https://www.google.com/search?q=cybersecurity+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>data analytics salary</t>
+          <t>cybersecurity vs data analytics</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=data+analytics+salary</t>
+          <t>https://www.google.com/search?q=cybersecurity+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>what is dbt labs</t>
+          <t>cloud vs data engineering</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=what+is+dbt+labs</t>
+          <t>https://www.google.com/search?q=cloud+vs+data+engineering</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>dbt 2.0</t>
+          <t>what is data pipeline management</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -9097,16 +9097,16 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>0.4478957915831664</v>
+        <v>0.5</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>suggest</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+2.0</t>
+          <t>https://www.google.com/search?q=what+is+data+pipeline+management</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>dbt mp</t>
+          <t>google analytics</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>0.4178356713426854</v>
+        <v>0.489</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+mp</t>
+          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>airbytehq/airbyte</t>
+          <t>banglarbhumi</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -9153,16 +9153,16 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>0.3537643257130241</v>
+        <v>0.48</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>https://github.com/airbytehq/airbyte</t>
+          <t>https://trends.google.com/trends/explore?q=banglarbhumi</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>power bi microsoft</t>
+          <t>social registry wb gov in</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>0.2975951903807615</v>
+        <v>0.45</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+microsoft</t>
+          <t>https://trends.google.com/trends/explore?q=social+registry+wb+gov+in</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>data and analytics</t>
+          <t>dbt mp</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>0.2975951903807615</v>
+        <v>0.42</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+and+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+mp</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>data science</t>
+          <t>fathom analytics</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>0.2975951903807615</v>
+        <v>0.39</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+science</t>
+          <t>https://trends.google.com/trends/explore?q=fathom+analytics</t>
         </is>
       </c>
     </row>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>mage-ai/mage-ai</t>
+          <t>airbytehq/airbyte</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>0.2827930875298557</v>
+        <v>0.3537643257130241</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>https://github.com/mage-ai/mage-ai</t>
+          <t>https://github.com/airbytehq/airbyte</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>software engineering</t>
+          <t>social security.wb.gov.in</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>0.2735470941883767</v>
+        <v>0.33</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=software+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=social+security.wb.gov.in</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt</t>
+          <t>heap analytics</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -9321,16 +9321,16 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>0.2214398972362162</v>
+        <v>0.33</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt</t>
+          <t>https://trends.google.com/trends/explore?q=heap+analytics</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>google analytics</t>
+          <t>data science</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0.1803607214428858</v>
+        <v>0.3</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+science</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>power bi que es y para que sirve</t>
+          <t>data analytics engineering</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>0.1773547094188377</v>
+        <v>0.3</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+que+es+y+para+que+sirve</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+engineering</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>engineering data management</t>
+          <t>microsoft power bi</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0.1743486973947896</v>
+        <v>0.3</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+power+bi</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ai data analytics</t>
+          <t>data and analytics</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>0.1623246492985972</v>
+        <v>0.3</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=ai+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+and+analytics</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>data engineering services</t>
+          <t>mage-ai/mage-ai</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -9461,16 +9461,16 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>0.156312625250501</v>
+        <v>0.2827930875298557</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
+          <t>https://github.com/mage-ai/mage-ai</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>power bi report</t>
+          <t>dbt-labs/dbt</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9489,16 +9489,16 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>0.1292585170340682</v>
+        <v>0.2214398972362162</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+report</t>
+          <t>https://github.com/dbt-labs/dbt</t>
         </is>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>evidentlyai/evidently</t>
+          <t>engineering data management</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -9517,16 +9517,16 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>0.1267687614154106</v>
+        <v>0.183</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>https://github.com/evidentlyai/evidently</t>
+          <t>https://trends.google.com/trends/explore?q=engineering+data+management</t>
         </is>
       </c>
     </row>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>data engineering platform</t>
+          <t>data engineering services</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -9545,7 +9545,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>0.1172344689378757</v>
+        <v>0.174</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+services</t>
         </is>
       </c>
     </row>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>dbt check</t>
+          <t>ai data analytics</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -9573,7 +9573,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>0.1142284569138277</v>
+        <v>0.159</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+check</t>
+          <t>https://trends.google.com/trends/explore?q=ai+data+analytics</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>business data analytics</t>
+          <t>power bi report</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>0.1142284569138277</v>
+        <v>0.135</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=business+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+report</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>social engineering</t>
+          <t>evidentlyai/evidently</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -9629,16 +9629,16 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>0.1142284569138277</v>
+        <v>0.1267687614154106</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=social+engineering</t>
+          <t>https://github.com/evidentlyai/evidently</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>download power bi</t>
+          <t>dbt check</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>0.1112224448897796</v>
+        <v>0.126</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=download+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+check</t>
         </is>
       </c>
     </row>
@@ -9676,7 +9676,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>0.1112224448897796</v>
+        <v>0.123</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=excel</t>
+          <t>https://trends.google.com/trends/explore?q=jobs</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9713,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>0.1112224448897796</v>
+        <v>0.12</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>evidence-dev/evidence</t>
+          <t>business data analytics</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -9741,16 +9741,16 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>0.1110491138630753</v>
+        <v>0.12</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>https://github.com/evidence-dev/evidence</t>
+          <t>https://trends.google.com/trends/explore?q=business+data+analytics</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>clearml/clearml</t>
+          <t>dbt pdf</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -9769,16 +9769,16 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>0.1099251349778215</v>
+        <v>0.12</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>https://github.com/clearml/clearml</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+pdf</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>dbt pdf</t>
+          <t>data analyst</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>0.1082164328657315</v>
+        <v>0.117</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+pdf</t>
+          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>data analyst</t>
+          <t>data engineer</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -9825,7 +9825,7 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>0.09919839679358719</v>
+        <v>0.117</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analyst</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineer</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>dbt status</t>
+          <t>data engineering platform</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>0.09919839679358716</v>
+        <v>0.117</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+status</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+platform</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>lightdash/lightdash</t>
+          <t>dbt status</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -9881,16 +9881,16 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>0.098235754571182</v>
+        <v>0.114</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>https://github.com/lightdash/lightdash</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+status</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>power bi ai</t>
+          <t>evidence-dev/evidence</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -9909,16 +9909,16 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>0.09318637274549098</v>
+        <v>0.1110491138630753</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
+          <t>https://github.com/evidence-dev/evidence</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>sql</t>
+          <t>clearml/clearml</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9937,16 +9937,16 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>0.09318637274549098</v>
+        <v>0.1099251349778215</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=sql</t>
+          <t>https://github.com/clearml/clearml</t>
         </is>
       </c>
     </row>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>power bi free</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>0.09318637274549098</v>
+        <v>0.108</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+free</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>power bi service</t>
+          <t>dashboard power bi</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9993,7 +9993,7 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>0.08416833667334669</v>
+        <v>0.108</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+service</t>
+          <t>https://trends.google.com/trends/explore?q=dashboard+power+bi</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>dax power bi</t>
+          <t>power bi price</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>0.0811623246492986</v>
+        <v>0.099</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+price</t>
         </is>
       </c>
     </row>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>big data analytics</t>
+          <t>lightdash/lightdash</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -10049,16 +10049,16 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>0.07214428857715431</v>
+        <v>0.098235754571182</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
+          <t>https://github.com/lightdash/lightdash</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>dax</t>
+          <t>power bi ai</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -10077,7 +10077,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>0.06913827655310621</v>
+        <v>0.096</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dax</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+ai</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>data engineering course</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -10105,7 +10105,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>0.06312625250501003</v>
+        <v>0.093</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
+          <t>https://trends.google.com/trends/explore?q=sql</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>power bi pro</t>
+          <t>business analytics</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>0.06312625250501003</v>
+        <v>0.09</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
+          <t>https://trends.google.com/trends/explore?q=business+analytics</t>
         </is>
       </c>
     </row>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>learn power bi</t>
+          <t>big data analytics</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -10161,7 +10161,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>0.06312625250501003</v>
+        <v>0.078</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+analytics</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>xo/dbtpl</t>
+          <t>dax</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -10189,16 +10189,16 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>0.06228448708427835</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>https://github.com/xo/dbtpl</t>
+          <t>https://trends.google.com/trends/explore?q=dax</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>data engineering solutions</t>
+          <t>dax power bi</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>0.06012024048096192</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=dax+power+bi</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>power bi online</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>0.06012024048096192</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
+          <t>https://trends.google.com/trends/explore?q=travel</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>app power bi</t>
+          <t>learn power bi</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10273,7 +10273,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0.06012024048096192</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>snowflake dbt</t>
+          <t>data engineering course</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -10301,7 +10301,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>0.05711422845691383</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+dbt</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+course</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>power query</t>
+          <t>data engineering solutions</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>0.05711422845691383</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+query</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+solutions</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>langwatch/langwatch</t>
+          <t>power bi online</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10357,16 +10357,16 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>0.05645585372217651</v>
+        <v>0.066</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>https://github.com/langwatch/langwatch</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+online</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>argilla-io/distilabel</t>
+          <t>power bi pro</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10385,16 +10385,16 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>0.05415972542801517</v>
+        <v>0.063</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>https://github.com/argilla-io/distilabel</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+pro</t>
         </is>
       </c>
     </row>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>data engineering tools</t>
+          <t>app power bi</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>0.05410821643286573</v>
+        <v>0.063</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+tools</t>
+          <t>https://trends.google.com/trends/explore?q=app+power+bi</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>SQLMesh/sqlmesh</t>
+          <t>software engineering</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -10441,16 +10441,16 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>0.05244164341769866</v>
+        <v>0.063</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>https://github.com/SQLMesh/sqlmesh</t>
+          <t>https://trends.google.com/trends/explore?q=software+engineering</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>microsoft learn</t>
+          <t>xo/dbtpl</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -10469,16 +10469,16 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>0.05110220440881763</v>
+        <v>0.06228448708427835</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=microsoft+learn</t>
+          <t>https://github.com/xo/dbtpl</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>spiceai/spiceai</t>
+          <t>snowflake dbt</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -10497,16 +10497,16 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>0.04919816149168055</v>
+        <v>0.06</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>https://github.com/spiceai/spiceai</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+dbt</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>data analytics course</t>
+          <t>power query</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -10525,7 +10525,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.06</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
+          <t>https://trends.google.com/trends/explore?q=power+query</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>data analytics services</t>
+          <t>langwatch/langwatch</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -10553,16 +10553,16 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.05645585372217651</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+services</t>
+          <t>https://github.com/langwatch/langwatch</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>power bi jobs</t>
+          <t>argilla-io/distilabel</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -10581,16 +10581,16 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.05415972542801517</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
+          <t>https://github.com/argilla-io/distilabel</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>learn microsoft power bi</t>
+          <t>data analytics services</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -10609,7 +10609,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>0.04809619238476953</v>
+        <v>0.05399999999999999</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=learn+microsoft+power+bi</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+services</t>
         </is>
       </c>
     </row>
@@ -10628,7 +10628,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>tableau</t>
+          <t>data analytics course</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -10637,7 +10637,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>0.04509018036072144</v>
+        <v>0.05399999999999999</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=tableau</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+course</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>data analytics software</t>
+          <t>data analytics platform</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>0.04509018036072144</v>
+        <v>0.05399999999999999</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+software</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+platform</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>slothflowlabs/duckle</t>
+          <t>microsoft learn power bi</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -10693,16 +10693,16 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>0.04107339983541738</v>
+        <v>0.05399999999999999</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>https://github.com/slothflowlabs/duckle</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+learn+power+bi</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>python</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10721,7 +10721,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>0.03907815631262525</v>
+        <v>0.05399999999999999</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=python</t>
+          <t>https://trends.google.com/trends/explore?q=music</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>power bi course</t>
+          <t>SQLMesh/sqlmesh</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -10749,16 +10749,16 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>0.03907815631262525</v>
+        <v>0.05244164341769866</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
+          <t>https://github.com/SQLMesh/sqlmesh</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>sodadata/soda-core</t>
+          <t>tableau</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -10777,16 +10777,16 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>0.03869698733516649</v>
+        <v>0.051</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>https://github.com/sodadata/soda-core</t>
+          <t>https://trends.google.com/trends/explore?q=tableau</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>elementary-data/elementary</t>
+          <t>microsoft learn</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10805,16 +10805,16 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>0.03835979366959035</v>
+        <v>0.051</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>https://github.com/elementary-data/elementary</t>
+          <t>https://trends.google.com/trends/explore?q=microsoft+learn</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>dbt training</t>
+          <t>power bi jobs</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -10833,7 +10833,7 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>0.03607214428857716</v>
+        <v>0.051</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+training</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+jobs</t>
         </is>
       </c>
     </row>
@@ -10852,7 +10852,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>power bi web</t>
+          <t>spiceai/spiceai</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -10861,16 +10861,16 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>0.03607214428857716</v>
+        <v>0.04919816149168055</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=power+bi+web</t>
+          <t>https://github.com/spiceai/spiceai</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>data analytics tools</t>
+          <t>data analytics software</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -10889,7 +10889,7 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>0.03006012024048096</v>
+        <v>0.048</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+tools</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+software</t>
         </is>
       </c>
     </row>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>power bi course</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -10917,16 +10917,16 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>0.02960881520582863</v>
+        <v>0.045</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+course</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>dbt-labs/dbt-utils</t>
+          <t>dbt training</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -10945,16 +10945,16 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>0.02862934789153604</v>
+        <v>0.045</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>https://github.com/dbt-labs/dbt-utils</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+training</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Hiflylabs/awesome-dbt</t>
+          <t>slothflowlabs/duckle</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>0.02742508480019269</v>
+        <v>0.04107339983541738</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>https://github.com/Hiflylabs/awesome-dbt</t>
+          <t>https://github.com/slothflowlabs/duckle</t>
         </is>
       </c>
     </row>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>data engineering consulting</t>
+          <t>study engineering</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -11001,7 +11001,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>0.02705410821643287</v>
+        <v>0.039</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=study+engineering</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>analytics engineer</t>
+          <t>power bi gateway</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -11029,7 +11029,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>0.02705410821643287</v>
+        <v>0.039</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=analytics+engineer</t>
+          <t>https://trends.google.com/trends/explore?q=power+bi+gateway</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Multiwoven/multiwoven</t>
+          <t>sodadata/soda-core</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -11057,7 +11057,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>0.02659012905686129</v>
+        <v>0.03869698733516649</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>https://github.com/Multiwoven/multiwoven</t>
+          <t>https://github.com/sodadata/soda-core</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Kaelio/ktx</t>
+          <t>elementary-data/elementary</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>0.025193183870903</v>
+        <v>0.03835979366959035</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>https://github.com/Kaelio/ktx</t>
+          <t>https://github.com/elementary-data/elementary</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>healthcare data analytics</t>
+          <t>financial data analytics</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>0.02404809619238477</v>
+        <v>0.036</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=healthcare+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=financial+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>duckdb/dbt-duckdb</t>
+          <t>data engineering consulting</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -11141,16 +11141,16 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>0.0214037693434759</v>
+        <v>0.033</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>https://github.com/duckdb/dbt-duckdb</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+consulting</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>astronomer/astronomer-cosmos</t>
+          <t>engineering analytics systems</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -11169,16 +11169,16 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>0.01994259679264597</v>
+        <v>0.033</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>https://github.com/astronomer/astronomer-cosmos</t>
+          <t>https://trends.google.com/trends/explore?q=engineering+analytics+systems</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>google data analytics certificate</t>
+          <t>exercise</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -11197,7 +11197,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>0.01803607214428858</v>
+        <v>0.03</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certificate</t>
+          <t>https://trends.google.com/trends/explore?q=exercise</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11216,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>snowflake data engineering</t>
+          <t>prompt engineering</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>0.01803607214428858</v>
+        <v>0.03</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=prompt+engineering</t>
         </is>
       </c>
     </row>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>dbt data engineering</t>
+          <t>NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -11253,16 +11253,16 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>0.01503006012024048</v>
+        <v>0.02960881520582863</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
+          <t>https://github.com/NVIDIA-AI-Blueprints/video-search-and-summarization</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>google data analytics professional certificate</t>
+          <t>dbt-labs/dbt-utils</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -11281,16 +11281,16 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.02862934789153604</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
+          <t>https://github.com/dbt-labs/dbt-utils</t>
         </is>
       </c>
     </row>
@@ -11300,7 +11300,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>data analytics masters</t>
+          <t>Hiflylabs/awesome-dbt</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -11309,16 +11309,16 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.02742508480019269</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+masters</t>
+          <t>https://github.com/Hiflylabs/awesome-dbt</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>data pipeline software</t>
+          <t>healthcare data analytics</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -11337,7 +11337,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.027</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
+          <t>https://trends.google.com/trends/explore?q=healthcare+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>data pipeline platform</t>
+          <t>what is social engineering</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.027</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
+          <t>https://trends.google.com/trends/explore?q=what+is+social+engineering</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>data analytics consulting</t>
+          <t>big data and analytics</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>0.01202404809619238</v>
+        <v>0.027</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+analytics+consulting</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+and+analytics</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>mikehasa/agentacct</t>
+          <t>data analytics solutions</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -11421,16 +11421,16 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>0.0112558456937559</v>
+        <v>0.027</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>https://github.com/mikehasa/agentacct</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+solutions</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>zhongyu09/openchatbi</t>
+          <t>Multiwoven/multiwoven</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -11449,7 +11449,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>0.01005158260241254</v>
+        <v>0.02659012905686129</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>https://github.com/zhongyu09/openchatbi</t>
+          <t>https://github.com/Multiwoven/multiwoven</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>TimeCopilot/timecopilot</t>
+          <t>Kaelio/ktx</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>0.009409308953696086</v>
+        <v>0.025193183870903</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>https://github.com/TimeCopilot/timecopilot</t>
+          <t>https://github.com/Kaelio/ktx</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>coursera</t>
+          <t>data engineering vs data analytics</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>0.009018036072144289</v>
+        <v>0.024</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=coursera</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+vs+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>data pipeline aws</t>
+          <t>duckdb/dbt-duckdb</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -11533,16 +11533,16 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>0.009018036072144289</v>
+        <v>0.0214037693434759</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+aws</t>
+          <t>https://github.com/duckdb/dbt-duckdb</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>machine learning data analytics</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11561,16 +11561,16 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>0.007337976436585513</v>
+        <v>0.021</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
+          <t>https://trends.google.com/trends/explore?q=machine+learning+data+analytics</t>
         </is>
       </c>
     </row>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>data pipeline solutions</t>
+          <t>snowflake data engineering</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.021</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
+          <t>https://trends.google.com/trends/explore?q=snowflake+data+engineering</t>
         </is>
       </c>
     </row>
@@ -11608,7 +11608,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>data pipeline monitoring</t>
+          <t>google data analytics certificate</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -11617,7 +11617,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.021</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certificate</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>masters in data analytics</t>
+          <t>data analytics degree</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.021</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=masters+in+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+degree</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>etl data pipeline</t>
+          <t>astronomer/astronomer-cosmos</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -11673,16 +11673,16 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>0.006012024048096191</v>
+        <v>0.01994259679264597</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>trends</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
+          <t>https://github.com/astronomer/astronomer-cosmos</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>upgini/upgini</t>
+          <t>dbt data engineering</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -11701,16 +11701,16 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>0.005459326014089879</v>
+        <v>0.018</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>https://github.com/upgini/upgini</t>
+          <t>https://trends.google.com/trends/explore?q=dbt+data+engineering</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>big data pipeline</t>
+          <t>data analytics consulting</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -11729,7 +11729,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.018</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+consulting</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>data engineering bootcamp</t>
+          <t>data pipeline development</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -11757,7 +11757,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.018</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+engineering+bootcamp</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+development</t>
         </is>
       </c>
     </row>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>google data analytics certification</t>
+          <t>data pipeline meaning</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -11785,7 +11785,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.015</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=google+data+analytics+certification</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+meaning</t>
         </is>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>dbt in data engineering</t>
+          <t>data pipeline platform</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -11813,7 +11813,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.015</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=dbt+in+data+engineering</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+platform</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>data pipeline examples</t>
+          <t>data analytics class</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.015</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=data+pipeline+examples</t>
+          <t>https://trends.google.com/trends/explore?q=data+analytics+class</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>what is big data analytics</t>
+          <t>google data analytics professional certificate</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>0.003006012024048096</v>
+        <v>0.015</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>https://trends.google.com/trends/explore?q=what+is+big+data+analytics</t>
+          <t>https://trends.google.com/trends/explore?q=google+data+analytics+professional+certificate</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Cesarjoquin/Marketing-Skills</t>
+          <t>data pipeline software</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11897,16 +11897,16 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>0.002713606165827028</v>
+        <v>0.015</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+software</t>
         </is>
       </c>
     </row>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>AngusKit/AngusKit</t>
+          <t>aws data pipeline</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -11925,16 +11925,16 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>0.002488810388776268</v>
+        <v>0.012</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>https://github.com/AngusKit/AngusKit</t>
+          <t>https://trends.google.com/trends/explore?q=aws+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>colossus-lab/openarg_backend</t>
+          <t>mikehasa/agentacct</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>0.002039218834674749</v>
+        <v>0.0112558456937559</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>https://github.com/colossus-lab/openarg_backend</t>
+          <t>https://github.com/mikehasa/agentacct</t>
         </is>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>zhongyu09/openchatbi</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11981,7 +11981,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>0.001974991469803103</v>
+        <v>0.01005158260241254</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
+          <t>https://github.com/zhongyu09/openchatbi</t>
         </is>
       </c>
     </row>
@@ -12000,7 +12000,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Chrisinho8/DACH-data-job-market</t>
+          <t>TimeCopilot/timecopilot</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -12009,7 +12009,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>0.001621740963009052</v>
+        <v>0.009409308953696086</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
+          <t>https://github.com/TimeCopilot/timecopilot</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>MUJTBA4F/attrition-insights-engineering</t>
+          <t>etl data pipeline</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -12037,16 +12037,16 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>0.001605684121791141</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>https://github.com/MUJTBA4F/attrition-insights-engineering</t>
+          <t>https://trends.google.com/trends/explore?q=etl+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>docwire/docwire</t>
+          <t>data pipeline solutions</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -12065,16 +12065,16 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>0.001525399915701584</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>https://github.com/docwire/docwire</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+solutions</t>
         </is>
       </c>
     </row>
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Shaf2665/Hermes-router</t>
+          <t>data pipeline monitoring</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -12093,16 +12093,16 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>0.00147722939204785</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>https://github.com/Shaf2665/Hermes-router</t>
+          <t>https://trends.google.com/trends/explore?q=data+pipeline+monitoring</t>
         </is>
       </c>
     </row>
@@ -12112,7 +12112,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>marieai/marie-ai</t>
+          <t>evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -12121,7 +12121,7 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>0.001268490456215001</v>
+        <v>0.007337976436585513</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>https://github.com/marieai/marie-ai</t>
+          <t>https://github.com/evelyyyyynnnnn/5.0-Ai-Engineering-Toolkit</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>ESIPFed/Geoweaver</t>
+          <t>big data pipeline</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -12149,16 +12149,16 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>0.00125243361499709</v>
+        <v>0.006</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>https://github.com/ESIPFed/Geoweaver</t>
+          <t>https://trends.google.com/trends/explore?q=big+data+pipeline</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>ServiceNow/SyGra</t>
+          <t>data engineering zoomcamp</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -12177,16 +12177,16 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>0.001188206250125444</v>
+        <v>0.006</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>trends</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>https://github.com/ServiceNow/SyGra</t>
+          <t>https://trends.google.com/trends/explore?q=data+engineering+zoomcamp</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>decisionbox-io/decisionbox-platform</t>
+          <t>upgini/upgini</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>0.001188206250125444</v>
+        <v>0.005459326014089879</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
+          <t>https://github.com/upgini/upgini</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>ellie886/Datalume</t>
+          <t>Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>0.001043694679164242</v>
+        <v>0.002713606165827028</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>https://github.com/ellie886/Datalume</t>
+          <t>https://github.com/Cesarjoquin/Marketing-Skills</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>social-media-skills/skills</t>
+          <t>AngusKit/AngusKit</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -12261,7 +12261,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>0.0009794673142925958</v>
+        <v>0.002488810388776268</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>https://github.com/social-media-skills/skills</t>
+          <t>https://github.com/AngusKit/AngusKit</t>
         </is>
       </c>
     </row>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>agentscope-ai/QwenPaw-Data</t>
+          <t>colossus-lab/openarg_backend</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>0.0009152399494209503</v>
+        <v>0.002039218834674749</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
+          <t>https://github.com/colossus-lab/openarg_backend</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -12317,7 +12317,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>0.0007707283784597475</v>
+        <v>0.001974991469803103</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
+          <t>https://github.com/hoangsonww/End-to-End-Data-Pipeline</t>
         </is>
       </c>
     </row>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>dataforgelabs/dataforge-core</t>
+          <t>Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>0.000706501013588102</v>
+        <v>0.001621740963009052</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>https://github.com/dataforgelabs/dataforge-core</t>
+          <t>https://github.com/Chrisinho8/DACH-data-job-market</t>
         </is>
       </c>
     </row>
@@ -12364,7 +12364,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Priyanshu-byte-coder/contextrot</t>
+          <t>MUJTBA4F/attrition-insights-engineering</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -12373,7 +12373,7 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>0.0005780462838448106</v>
+        <v>0.001605684121791141</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
+          <t>https://github.com/MUJTBA4F/attrition-insights-engineering</t>
         </is>
       </c>
     </row>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>pella-labs/pellametric</t>
+          <t>docwire/docwire</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>0.0004495915541015194</v>
+        <v>0.001525399915701584</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>https://github.com/pella-labs/pellametric</t>
+          <t>https://github.com/docwire/docwire</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>Shaf2665/Hermes-router</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -12429,7 +12429,7 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>0.000433534712883608</v>
+        <v>0.00147722939204785</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+          <t>https://github.com/Shaf2665/Hermes-router</t>
         </is>
       </c>
     </row>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>marieai/marie-ai</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>0.0003693073480119624</v>
+        <v>0.001268490456215001</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+          <t>https://github.com/marieai/marie-ai</t>
         </is>
       </c>
     </row>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Dreamerol/Dreamerol</t>
+          <t>ESIPFed/Geoweaver</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>0.0003211368243582281</v>
+        <v>0.00125243361499709</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/Dreamerol</t>
+          <t>https://github.com/ESIPFed/Geoweaver</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>nirholas/bnbchain-mcp</t>
+          <t>ServiceNow/SyGra</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -12513,7 +12513,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>0.0002569094594865825</v>
+        <v>0.001188206250125444</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>https://github.com/nirholas/bnbchain-mcp</t>
+          <t>https://github.com/ServiceNow/SyGra</t>
         </is>
       </c>
     </row>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Tony405-spec/feature-engineering-healthcare</t>
+          <t>decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>0.0001284547297432913</v>
+        <v>0.001188206250125444</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>https://github.com/Tony405-spec/feature-engineering-healthcare</t>
+          <t>https://github.com/decisionbox-io/decisionbox-platform</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>exmergo/dex</t>
+          <t>ellie886/Datalume</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>0.0001123978885253799</v>
+        <v>0.001059751520382153</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>https://github.com/exmergo/dex</t>
+          <t>https://github.com/ellie886/Datalume</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>social-media-skills/skills</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -12597,7 +12597,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>0.0001123978885253799</v>
+        <v>0.0009794673142925958</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+          <t>https://github.com/social-media-skills/skills</t>
         </is>
       </c>
     </row>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>9.634104730746844e-05</v>
+        <v>0.0009152399494209503</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+          <t>https://github.com/agentscope-ai/QwenPaw-Data</t>
         </is>
       </c>
     </row>
@@ -12644,7 +12644,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>A list of articles on how data teams built their analytics agents</t>
+          <t>center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -12653,16 +12653,16 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>0</v>
+        <v>0.0007707283784597475</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>https://github.com/GetCassis/analytics-agent-articles</t>
+          <t>https://github.com/center-for-threat-informed-defense/summiting-the-pyramid</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Show HN: The Analyst (A data science analytics simulator)</t>
+          <t>dataforgelabs/dataforge-core</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -12681,16 +12681,16 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>0</v>
+        <v>0.000706501013588102</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>https://theanalyst.dev</t>
+          <t>https://github.com/dataforgelabs/dataforge-core</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Designing a Dbt Pipeline for Consent Withdrawal</t>
+          <t>Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -12709,16 +12709,16 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>0</v>
+        <v>0.0005780462838448106</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>hn</t>
+          <t>github</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>https://kore-nordmann.de/blog/designing-a-dbt-pipeline-for-consent-withdrawal.html</t>
+          <t>https://github.com/Priyanshu-byte-coder/contextrot</t>
         </is>
       </c>
     </row>
@@ -12728,7 +12728,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Dreamerol/ALLSTATS</t>
+          <t>pella-labs/pellametric</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -12737,7 +12737,7 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>0</v>
+        <v>0.0004495915541015194</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>https://github.com/Dreamerol/ALLSTATS</t>
+          <t>https://github.com/pella-labs/pellametric</t>
         </is>
       </c>
     </row>
@@ -12756,25 +12756,417 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
+          <t>Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>0.000433534712883608</v>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>https://github.com/Victor-Kipruto-Rop/Real_Time_Transaction_Streaming-MPESA-</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>0.0003693073480119624</v>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>https://github.com/AmirhosseinHonardoust/Coffee-Shop-Profit-Predictor</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Dreamerol/Dreamerol</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>0.0003211368243582281</v>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/Dreamerol</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>nirholas/bnbchain-mcp</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>0.0002569094594865825</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>https://github.com/nirholas/bnbchain-mcp</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Tony405-spec/feature-engineering-healthcare</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>0.0001284547297432913</v>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>https://github.com/Tony405-spec/feature-engineering-healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>0.0001123978885253799</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>https://github.com/Victor-Kipruto-Rop/medallion-lakehouse-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>exmergo/dex</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>0.0001123978885253799</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>https://github.com/exmergo/dex</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>9.634104730746844e-05</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>https://github.com/analyticsdurgesh/Snowflake_DBT_Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Show HN: The Analyst (A data science analytics simulator)</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>0</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>https://theanalyst.dev</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>machine learning algorithms</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>0</v>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=machine+learning+algorithms</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Designing a Dbt Pipeline for Consent Withdrawal</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>0</v>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>https://kore-nordmann.de/blog/designing-a-dbt-pipeline-for-consent-withdrawal.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>data warehouse design</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>0</v>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>trends</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>https://trends.google.com/trends/explore?q=data+warehouse+design</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>0</v>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>https://github.com/Dreamerol/ALLSTATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
           <t>Assembling context for analytics agents from existing data stacks</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>NEW / SPIKE</t>
-        </is>
-      </c>
-      <c r="D418" t="n">
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
         <v>0</v>
       </c>
-      <c r="E418" t="inlineStr">
+      <c r="E431" t="inlineStr">
         <is>
           <t>hn</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr">
+      <c r="F431" t="inlineStr">
         <is>
           <t>https://blog.getcassis.com/a-blank-beats-a-guess/</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>A list of articles on how data teams built their analytics agents</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>NEW / SPIKE</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>0</v>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>hn</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>https://github.com/GetCassis/analytics-agent-articles</t>
         </is>
       </c>
     </row>
